--- a/output/HS_Code_Summary_Sonavox_Technology_CZ_TECGO26080029.xlsx
+++ b/output/HS_Code_Summary_Sonavox_Technology_CZ_TECGO26080029.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="198">
   <si>
     <t xml:space="preserve">HS CODE SUMMARY – Sonavox Technology CZ s.r.o.</t>
   </si>
@@ -163,177 +163,162 @@
     <t xml:space="preserve">Zařazení dle ZISZ 30-0292-2016 (kmitací cívka = ostatní tlumivky).</t>
   </si>
   <si>
-    <t xml:space="preserve">8518900090</t>
+    <t xml:space="preserve">8518900000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ocelová deska (front plate) – součást autoreproduktoru; Středící membrána (spider) – naimpregnovaná textilie, součást autoreproduktoru; Membrána s vlnkou (cone) – membrána elektrodynamického reproduktoru; Kontakt / vývod (terminal) – část autoreproduktoru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Části a součásti reproduktorů. Přípona DK 00 a zařazení terminalu i front plate pod tento kód dle předchozího celního prohlášení Sonavox (viz list Zdroje).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3926909790</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plastové těsnění (gasket) – ostatní výrobky z plastů; Plastový kalibr (gauge) – montážní přípravek, ostatní výrobky z plastů</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ostatní výrobky z plastů. Gasket + Gauge na jednom řádku, DK 90 – potvrzeno předchozím celním prohlášením Sonavox.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3921909090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plastová membrána (vodotěsná membrána) – ochranná membrána reproduktoru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ostatní desky, listy, fólie a pásy z plastů.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7318159519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matice / vložka (nut, insert) – závitové zboží ze železa nebo oceli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spojovací materiál ze železa/oceli, původ ČÍNA – viz list Poznámky.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7413000090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kabelový svazek – splétané lanko, slitina měď (78 %) a cín, neizolované</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Splétaná lanka z mědi, neizolovaná.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mezisoučet – Suzhou Sonavox International Trading Co., Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suzhou Sonavox Electronics Co., Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CZ20260725-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magnetický obvod (ceramics circle) – feritové jádro (nezmagnetované), součást autoreproduktoru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8518210000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reproduktor (autoreproduktor), jediný v jedné skříni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kompletní autoreproduktor, jediný v jedné skříni.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mezisoučet – Suzhou Sonavox Electronics Co., Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suzhou Yanlong Electronic Product Co., Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CZ20260725-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Membrána s vlnkou (cone) – membrána elektrodynamického reproduktoru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mezisoučet – Suzhou Yanlong Electronic Product Co., Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CELKEM ZÁSILKA / TOTAL SHIPMENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kontrola / cross-check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ze souhrnu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z dokladů</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rozdíl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Množství celkem vs. součet faktur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Čistá hmotnost celkem (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hrubá hmotnost celkem (kg) vs. FCR/SMGS 24 133 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Celní hodnota celkem (EUR) vs. součet faktur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invoice No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description of Goods (EN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity (pcs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net weight (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross weight (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customs value (EUR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">010-KD1622S-3.8A-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voice coil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">040-62E4-CR-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Front plate</t>
   </si>
   <si>
     <t xml:space="preserve">Ocelová deska (front plate) – součást autoreproduktoru</t>
   </si>
   <si>
-    <t xml:space="preserve">Přípona 90 dle podkladu SONAVOX; ocelový díl, ale zařazen v kap. 85 – mimo CBAM.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8518900000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Středící membrána (spider) – naimpregnovaná textilie, součást autoreproduktoru; Membrána s vlnkou (cone) – membrána elektrodynamického reproduktoru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Části a součásti reproduktorů.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3926909790</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plastové těsnění (gasket) – ostatní výrobky z plastů; Plastový kalibr (gauge) – montážní přípravek, ostatní výrobky z plastů</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ostatní výrobky z plastů.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3921909090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plastová membrána (vodotěsná membrána) – ochranná membrána reproduktoru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ostatní desky, listy, fólie a pásy z plastů.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7409390000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kontakt / vývod (terminal) – z mědi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desky/pásy ze slitin mědi – kap. 74 není v příloze I CBAM.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7318159519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matice / vložka (nut, insert) – závitové zboží ze železa nebo oceli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spojovací materiál ze železa/oceli, původ ČÍNA – viz list Poznámky.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7413000090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kabelový svazek – splétané lanko, slitina měď (78 %) a cín, neizolované</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Splétaná lanka z mědi, neizolovaná.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mezisoučet – Suzhou Sonavox International Trading Co., Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suzhou Sonavox Electronics Co., Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CZ20260725-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magnetický obvod (ceramics circle) – feritové jádro (nezmagnetované), součást autoreproduktoru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8518210000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reproduktor (autoreproduktor), jediný v jedné skříni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kompletní autoreproduktor, jediný v jedné skříni.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mezisoučet – Suzhou Sonavox Electronics Co., Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suzhou Yanlong Electronic Product Co., Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CZ20260725-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Membrána s vlnkou (cone) – membrána elektrodynamického reproduktoru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mezisoučet – Suzhou Yanlong Electronic Product Co., Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CELKEM ZÁSILKA / TOTAL SHIPMENT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kontrola / cross-check</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ze souhrnu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z dokladů</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rozdíl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Množství celkem vs. součet faktur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Čistá hmotnost celkem (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hrubá hmotnost celkem (kg) vs. FCR/SMGS 24 133 kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Celní hodnota celkem (EUR) vs. součet faktur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invoice No.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Part Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description of Goods (EN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HS code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity (pcs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net weight (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gross weight (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customs value (EUR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">010-KD1622S-3.8A-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voice coil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">040-62E4-CR-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Front plate</t>
-  </si>
-  <si>
     <t xml:space="preserve">040-80I6-CRB-CZ</t>
   </si>
   <si>
@@ -394,6 +379,9 @@
     <t xml:space="preserve">Terminal</t>
   </si>
   <si>
+    <t xml:space="preserve">Kontakt / vývod (terminal) – část autoreproduktoru</t>
+  </si>
+  <si>
     <t xml:space="preserve">181-35113-2SN-CZ</t>
   </si>
   <si>
@@ -493,10 +481,13 @@
     <t xml:space="preserve">Označení dílu obsahuje „-AL-“, což naznačuje HLINÍK, avšak podklad SONAVOX (e-mail „SONAVOX HS KODY“) přiřazuje „Insert (nut)“ kód 7318 15 95 19 (železo/ocel). Hliníková matice by patřila pod 7616 10 00. Zařazení má přímý dopad: 7318 = antidumping ANO + CBAM ANO; 7616 = antidumping NE + CBAM ANO. V souhrnu je konzervativně použito 7318 15 95 19. NUTNO POTVRDIT MATERIÁL U DODAVATELE.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nekonzistentní 10místné přípony u 8518 90 00 v podkladu SONAVOX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Referenční tabulka HS kódů od Sonavoxu používá pro části reproduktorů souběžně 8518 9000 00, 8518 9000 40, 8518 9000 90 i 8518 9000 99. Na úrovni KN8 jde vždy o 8518 90 00. V souhrnu je zachováno rozlišení dle podkladu (Front plate = ...90, ostatní části = ...00), ale platnou národní/TARIC příponu je nutno ověřit v TARIC CZ – při proclení musí být použit jeden platný 10místný kód.</t>
+    <t xml:space="preserve">VYŘEŠENO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Přípona u 8518 90 00 = DK 00 (opraveno dle předchozích celních prohlášení)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referenční tabulka SONAVOX uvádí u částí reproduktorů souběžně přípony 00, 40, 90 i 99. Ve dvou předchozích celních prohlášeních Sonavox je však pro VŠECHNY části reproduktorů použito jednotně 8518 90 00 s doplňkovým kódem DK 00 – včetně Front plate („Front plate – deska“), T-yoke, Cone, Spider, Dust cap a Bracket. Front plate byl proto v tomto souhrnu OPRAVEN z 8518 9000 90 na 8518 9000 00. Přípony 40 / 90 / 99 z tabulky SONAVOX se v praxi nepoužívají.</t>
   </si>
   <si>
     <t xml:space="preserve">Waterproof membrane – kód přiřazen odvozením</t>
@@ -505,10 +496,10 @@
     <t xml:space="preserve">Položka 9 (J2-10X002-0001-CZ, Waterproof membrane, 210 000 ks, 8 820,00 EUR) není v referenční tabulce SONAVOX uvedena pod tímto názvem. Byl použit kód 3921 90 90 90 podle nejbližší položky „Protective membrane plast / Plastová membrána“. Doporučeno potvrdit u dodavatele.</t>
   </si>
   <si>
-    <t xml:space="preserve">Terminal – kód přiřazen odvozením</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Položky 10–13 (Terminal, celkem 600 000 ks, 9 380,00 EUR) byly zařazeny pod 7409 39 00 podle položky „Pin, lug / kontakt“ z tabulky SONAVOX. Pokud jsou terminály pocínované/potažené nebo tvarované lisováním, může přicházet v úvahu jiné zařazení (např. 8536 90). Doporučeno potvrdit.</t>
+    <t xml:space="preserve">Terminal – OPRAVENO z 7409 39 00 na 8518 90 00 00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Položky 10–13 (Terminal, celkem 600 000 ks, 9 380,00 EUR) byly původně zařazeny pod 7409 39 00 podle položky „Pin, lug / kontakt“ z tabulky SONAVOX. Předchozí celní prohlášení Sonavox však deklaruje „terminal – části reproduktorů“ pod 8518 90 00 DK 00. Zařazení bylo opraveno na 8518 90 00 00, což je i věcně správnější (hotový díl určený výhradně pro reproduktor = část zboží čísla 8518 dle pozn. 2 ke třídě XVI; 7409 je naopak polotovar – desky a pásy z mědi).</t>
   </si>
   <si>
     <t xml:space="preserve">NESROVNALOST</t>
@@ -544,6 +535,12 @@
     <t xml:space="preserve">Packing list CZ20260725-2 (Yanlong) uvádí ETD 29.07.2026 / ETA 29.08.2026; FCR byl však vystaven 04.08.2026 a vlak má č. V.WB2026/08/05 (05.08.2026). U zbylých dvou sad dokladů jsou ETD/ETA prázdné. Doporučeno sjednotit.</t>
   </si>
   <si>
+    <t xml:space="preserve">Potvrzeno předchozími celními prohlášeními Sonavox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z dvou předchozích celních prohlášení na obdobné zásilky Sonavox byly potvrzeny tyto kódy: Cone, Spider, Dust cap, T-yoke, Front plate, Bracket, Speaker component i Terminal = 8518 90 00 DK 00; Car speaker = 8518 21 00 DK 00; Harness / kabelový svazek = 7413 00 00 DK 90; Gasket (plastové těsnění) + Gauge (plastový kalibr) společně na jednom řádku = 3926 90 97 DK 90. Potvrzen je rovněž postup slučování více komponent pod jeden kód na jeden řádek.</t>
+  </si>
+  <si>
     <t xml:space="preserve">OK</t>
   </si>
   <si>
@@ -613,10 +610,16 @@
     <t xml:space="preserve">Referenční tabulka HS kódů s českými popisy (Ing. Michaela Ryan, Sonavox Technology CZ) – zdroj HS kódů a českých popisů</t>
   </si>
   <si>
+    <t xml:space="preserve">Předchozí celní prohlášení Sonavox (2 ks)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Screenshoty položek dřívějších celních prohlášení na obdobné zásilky – zdroj potvrzení kódů 8518 90 00 DK 00, 8518 21 00 DK 00, 7413 00 00 DK 90 a 3926 90 97 DK 90</t>
+  </si>
+  <si>
     <t xml:space="preserve">POZOR</t>
   </si>
   <si>
-    <t xml:space="preserve">Faktury ANI packing listy neobsahují žádné HS kódy. Všechny HS kódy v tomto souhrnu jsou přiřazeny podle referenční tabulky z e-mailu „SONAVOX HS KODY“ na základě názvu dílu; položky bez přímé shody jsou označeny na listu Poznámky &amp; flagy jako „K OVĚŘENÍ“.</t>
+    <t xml:space="preserve">Faktury ANI packing listy neobsahují žádné HS kódy. Kódy v tomto souhrnu pocházejí z referenční tabulky „SONAVOX HS KODY“ a z předchozích celních prohlášení Sonavox. Kde se oba zdroje liší, má přednost celní prohlášení (Front plate, Terminal). Zbývající nepotvrzené položky jsou na listu Poznámky &amp; flagy označeny jako „K OVĚŘENÍ“: Nut / Spring nut (materiál) a Waterproof membrane. Voice coil je podložen závaznou informací o sazebním zařazení ZISZ 30-0292-2016.</t>
   </si>
 </sst>
 </file>
@@ -1210,7 +1213,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
@@ -1415,7 +1418,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
         <v>39</v>
       </c>
@@ -1430,19 +1433,19 @@
       </c>
       <c r="E19" s="9" t="n">
         <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A19,'Line items'!$F$2:$F$25,$C19)</f>
-        <v>92400</v>
+        <v>778000</v>
       </c>
       <c r="F19" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A19,'Line items'!$F$2:$F$25,$C19)</f>
-        <v>8460.5</v>
+        <v>8806.4</v>
       </c>
       <c r="G19" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A19,'Line items'!$F$2:$F$25,$C19)</f>
-        <v>8600.91</v>
+        <v>8990.91</v>
       </c>
       <c r="H19" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A19,'Line items'!$F$2:$F$25,$C19)</f>
-        <v>12384.46</v>
+        <v>32182.14</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>22</v>
@@ -1472,19 +1475,19 @@
       </c>
       <c r="E20" s="9" t="n">
         <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A20,'Line items'!$F$2:$F$25,$C20)</f>
-        <v>85600</v>
+        <v>9960</v>
       </c>
       <c r="F20" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A20,'Line items'!$F$2:$F$25,$C20)</f>
-        <v>45.9</v>
+        <v>103.09</v>
       </c>
       <c r="G20" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A20,'Line items'!$F$2:$F$25,$C20)</f>
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="H20" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A20,'Line items'!$F$2:$F$25,$C20)</f>
-        <v>10417.68</v>
+        <v>1378.1</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>22</v>
@@ -1514,19 +1517,19 @@
       </c>
       <c r="E21" s="9" t="n">
         <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A21,'Line items'!$F$2:$F$25,$C21)</f>
-        <v>9960</v>
+        <v>210000</v>
       </c>
       <c r="F21" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A21,'Line items'!$F$2:$F$25,$C21)</f>
-        <v>103.09</v>
+        <v>30.24</v>
       </c>
       <c r="G21" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A21,'Line items'!$F$2:$F$25,$C21)</f>
-        <v>128</v>
+        <v>40</v>
       </c>
       <c r="H21" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A21,'Line items'!$F$2:$F$25,$C21)</f>
-        <v>1378.1</v>
+        <v>8820</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>22</v>
@@ -1542,45 +1545,45 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="13" t="n">
         <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A22,'Line items'!$F$2:$F$25,$C22)</f>
         <v>210000</v>
       </c>
-      <c r="F22" s="10" t="n">
+      <c r="F22" s="14" t="n">
         <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A22,'Line items'!$F$2:$F$25,$C22)</f>
-        <v>30.24</v>
-      </c>
-      <c r="G22" s="10" t="n">
+        <v>312.3</v>
+      </c>
+      <c r="G22" s="14" t="n">
         <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A22,'Line items'!$F$2:$F$25,$C22)</f>
-        <v>40</v>
-      </c>
-      <c r="H22" s="10" t="n">
+        <v>325.5</v>
+      </c>
+      <c r="H22" s="14" t="n">
         <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A22,'Line items'!$F$2:$F$25,$C22)</f>
-        <v>8820</v>
-      </c>
-      <c r="I22" s="7" t="s">
+        <v>13140</v>
+      </c>
+      <c r="I22" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="J22" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="L22" s="7" t="s">
+      <c r="J22" s="15" t="s">
         <v>56</v>
+      </c>
+      <c r="K22" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1591,26 +1594,26 @@
         <v>40</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E23" s="9" t="n">
         <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A23,'Line items'!$F$2:$F$25,$C23)</f>
-        <v>600000</v>
+        <v>51200</v>
       </c>
       <c r="F23" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A23,'Line items'!$F$2:$F$25,$C23)</f>
-        <v>300</v>
+        <v>235.52</v>
       </c>
       <c r="G23" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A23,'Line items'!$F$2:$F$25,$C23)</f>
-        <v>330</v>
+        <v>250</v>
       </c>
       <c r="H23" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A23,'Line items'!$F$2:$F$25,$C23)</f>
-        <v>9380</v>
+        <v>8120.32</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>22</v>
@@ -1622,79 +1625,65 @@
         <v>43</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="D24" s="11" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="E24" s="13" t="n">
-        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A24,'Line items'!$F$2:$F$25,$C24)</f>
-        <v>210000</v>
-      </c>
-      <c r="F24" s="14" t="n">
-        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A24,'Line items'!$F$2:$F$25,$C24)</f>
-        <v>312.3</v>
-      </c>
-      <c r="G24" s="14" t="n">
-        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A24,'Line items'!$F$2:$F$25,$C24)</f>
-        <v>325.5</v>
-      </c>
-      <c r="H24" s="14" t="n">
-        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A24,'Line items'!$F$2:$F$25,$C24)</f>
-        <v>13140</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J24" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="K24" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="L24" s="11" t="s">
-        <v>63</v>
-      </c>
+      <c r="E24" s="18" t="n">
+        <f aca="false">SUM(E18:E23)</f>
+        <v>1324160</v>
+      </c>
+      <c r="F24" s="19" t="n">
+        <f aca="false">SUM(F18:F23)</f>
+        <v>9574.05</v>
+      </c>
+      <c r="G24" s="19" t="n">
+        <f aca="false">SUM(G18:G23)</f>
+        <v>9950.74</v>
+      </c>
+      <c r="H24" s="19" t="n">
+        <f aca="false">SUM(H18:H23)</f>
+        <v>73481.56</v>
+      </c>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="C25" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>64</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>65</v>
       </c>
       <c r="E25" s="9" t="n">
         <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A25,'Line items'!$F$2:$F$25,$C25)</f>
-        <v>51200</v>
+        <v>19152</v>
       </c>
       <c r="F25" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A25,'Line items'!$F$2:$F$25,$C25)</f>
-        <v>235.52</v>
+        <v>11299.68</v>
       </c>
       <c r="G25" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A25,'Line items'!$F$2:$F$25,$C25)</f>
-        <v>250</v>
+        <v>11688.8</v>
       </c>
       <c r="H25" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A25,'Line items'!$F$2:$F$25,$C25)</f>
-        <v>8120.32</v>
+        <v>19918.08</v>
       </c>
       <c r="I25" s="7" t="s">
         <v>22</v>
@@ -1706,107 +1695,107 @@
         <v>43</v>
       </c>
       <c r="L25" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17" t="s">
+      <c r="E26" s="9" t="n">
+        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A26,'Line items'!$F$2:$F$25,$C26)</f>
+        <v>2016</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A26,'Line items'!$F$2:$F$25,$C26)</f>
+        <v>1149.12</v>
+      </c>
+      <c r="G26" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A26,'Line items'!$F$2:$F$25,$C26)</f>
+        <v>1219.04</v>
+      </c>
+      <c r="H26" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A26,'Line items'!$F$2:$F$25,$C26)</f>
+        <v>5140.8</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L26" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E26" s="18" t="n">
-        <f aca="false">SUM(E18:E25)</f>
-        <v>1324160</v>
-      </c>
-      <c r="F26" s="19" t="n">
-        <f aca="false">SUM(F18:F25)</f>
-        <v>9574.05</v>
-      </c>
-      <c r="G26" s="19" t="n">
-        <f aca="false">SUM(G18:G25)</f>
-        <v>9950.74</v>
-      </c>
-      <c r="H26" s="19" t="n">
-        <f aca="false">SUM(H18:H25)</f>
-        <v>73481.56</v>
-      </c>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-    </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E27" s="9" t="n">
-        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A27,'Line items'!$F$2:$F$25,$C27)</f>
-        <v>19152</v>
-      </c>
-      <c r="F27" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A27,'Line items'!$F$2:$F$25,$C27)</f>
-        <v>11299.68</v>
-      </c>
-      <c r="G27" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A27,'Line items'!$F$2:$F$25,$C27)</f>
-        <v>11688.8</v>
-      </c>
-      <c r="H27" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A27,'Line items'!$F$2:$F$25,$C27)</f>
-        <v>19918.08</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="L27" s="7" t="s">
-        <v>50</v>
-      </c>
+      <c r="E27" s="18" t="n">
+        <f aca="false">SUM(E25:E26)</f>
+        <v>21168</v>
+      </c>
+      <c r="F27" s="19" t="n">
+        <f aca="false">SUM(F25:F26)</f>
+        <v>12448.8</v>
+      </c>
+      <c r="G27" s="19" t="n">
+        <f aca="false">SUM(G25:G26)</f>
+        <v>12907.84</v>
+      </c>
+      <c r="H27" s="19" t="n">
+        <f aca="false">SUM(H25:H26)</f>
+        <v>25058.88</v>
+      </c>
+      <c r="I27" s="16"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C28" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>71</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>72</v>
       </c>
       <c r="E28" s="9" t="n">
         <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A28,'Line items'!$F$2:$F$25,$C28)</f>
-        <v>2016</v>
+        <v>43760</v>
       </c>
       <c r="F28" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A28,'Line items'!$F$2:$F$25,$C28)</f>
-        <v>1149.12</v>
+        <v>957</v>
       </c>
       <c r="G28" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A28,'Line items'!$F$2:$F$25,$C28)</f>
-        <v>1219.04</v>
+        <v>1274.42</v>
       </c>
       <c r="H28" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A28,'Line items'!$F$2:$F$25,$C28)</f>
-        <v>5140.8</v>
+        <v>20830.64</v>
       </c>
       <c r="I28" s="7" t="s">
         <v>22</v>
@@ -1818,7 +1807,7 @@
         <v>43</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1826,151 +1815,113 @@
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
       <c r="D29" s="17" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E29" s="18" t="n">
-        <f aca="false">SUM(E27:E28)</f>
-        <v>21168</v>
+        <f aca="false">SUM(E28:E28)</f>
+        <v>43760</v>
       </c>
       <c r="F29" s="19" t="n">
-        <f aca="false">SUM(F27:F28)</f>
-        <v>12448.8</v>
+        <f aca="false">SUM(F28:F28)</f>
+        <v>957</v>
       </c>
       <c r="G29" s="19" t="n">
-        <f aca="false">SUM(G27:G28)</f>
-        <v>12907.84</v>
+        <f aca="false">SUM(G28:G28)</f>
+        <v>1274.42</v>
       </c>
       <c r="H29" s="19" t="n">
-        <f aca="false">SUM(H27:H28)</f>
-        <v>25058.88</v>
+        <f aca="false">SUM(H28:H28)</f>
+        <v>20830.64</v>
       </c>
       <c r="I29" s="16"/>
       <c r="J29" s="16"/>
       <c r="K29" s="16"/>
       <c r="L29" s="16"/>
     </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E30" s="22" t="n">
+        <f aca="false">E24+E27+E29</f>
+        <v>1389088</v>
+      </c>
+      <c r="F30" s="23" t="n">
+        <f aca="false">F24+F27+F29</f>
+        <v>22979.85</v>
+      </c>
+      <c r="G30" s="23" t="n">
+        <f aca="false">G24+G27+G29</f>
+        <v>24133</v>
+      </c>
+      <c r="H30" s="23" t="n">
+        <f aca="false">H24+H27+H29</f>
+        <v>119371.08</v>
+      </c>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="C32" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C30" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D30" s="7" t="s">
+      <c r="D32" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E30" s="9" t="n">
-        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A30,'Line items'!$F$2:$F$25,$C30)</f>
-        <v>43760</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A30,'Line items'!$F$2:$F$25,$C30)</f>
-        <v>957</v>
-      </c>
-      <c r="G30" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A30,'Line items'!$F$2:$F$25,$C30)</f>
-        <v>1274.42</v>
-      </c>
-      <c r="H30" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A30,'Line items'!$F$2:$F$25,$C30)</f>
-        <v>20830.64</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J30" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K30" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="L30" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="16"/>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="17" t="s">
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E31" s="18" t="n">
-        <f aca="false">SUM(E30:E30)</f>
-        <v>43760</v>
-      </c>
-      <c r="F31" s="19" t="n">
-        <f aca="false">SUM(F30:F30)</f>
-        <v>957</v>
-      </c>
-      <c r="G31" s="19" t="n">
-        <f aca="false">SUM(G30:G30)</f>
-        <v>1274.42</v>
-      </c>
-      <c r="H31" s="19" t="n">
-        <f aca="false">SUM(H30:H30)</f>
-        <v>20830.64</v>
-      </c>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="20"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="21" t="s">
+      <c r="B33" s="24" t="n">
+        <f aca="false">E30</f>
+        <v>1389088</v>
+      </c>
+      <c r="C33" s="24" t="n">
+        <v>1389088</v>
+      </c>
+      <c r="D33" s="24" t="n">
+        <f aca="false">B33-C33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E32" s="22" t="n">
-        <f aca="false">E26+E29+E31</f>
-        <v>1389088</v>
-      </c>
-      <c r="F32" s="23" t="n">
-        <f aca="false">F26+F29+F31</f>
+      <c r="B34" s="24" t="n">
+        <f aca="false">F30</f>
         <v>22979.85</v>
       </c>
-      <c r="G32" s="23" t="n">
-        <f aca="false">G26+G29+G31</f>
-        <v>24133</v>
-      </c>
-      <c r="H32" s="23" t="n">
-        <f aca="false">H26+H29+H31</f>
-        <v>119371.08</v>
-      </c>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="20"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>83</v>
+      <c r="C34" s="24" t="n">
+        <v>22979.85</v>
+      </c>
+      <c r="D34" s="24" t="n">
+        <f aca="false">B34-C34</f>
+        <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B35" s="24" t="n">
-        <f aca="false">E32</f>
-        <v>1389088</v>
+        <f aca="false">G30</f>
+        <v>24133</v>
       </c>
       <c r="C35" s="24" t="n">
-        <v>1389088</v>
+        <v>24133</v>
       </c>
       <c r="D35" s="24" t="n">
         <f aca="false">B35-C35</f>
@@ -1979,49 +1930,17 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B36" s="24" t="n">
-        <f aca="false">F32</f>
-        <v>22979.85</v>
+        <f aca="false">H30</f>
+        <v>119371.08</v>
       </c>
       <c r="C36" s="24" t="n">
-        <v>22979.85</v>
+        <v>119371.08</v>
       </c>
       <c r="D36" s="24" t="n">
         <f aca="false">B36-C36</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B37" s="24" t="n">
-        <f aca="false">G32</f>
-        <v>24133</v>
-      </c>
-      <c r="C37" s="24" t="n">
-        <v>24133</v>
-      </c>
-      <c r="D37" s="24" t="n">
-        <f aca="false">B37-C37</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B38" s="24" t="n">
-        <f aca="false">H32</f>
-        <v>119371.08</v>
-      </c>
-      <c r="C38" s="24" t="n">
-        <v>119371.08</v>
-      </c>
-      <c r="D38" s="24" t="n">
-        <f aca="false">B38-C38</f>
         <v>0</v>
       </c>
     </row>
@@ -2057,37 +1976,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E1" s="25" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F1" s="25" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="G1" s="25" t="s">
         <v>30</v>
       </c>
       <c r="H1" s="25" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="I1" s="25" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="J1" s="25" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K1" s="25" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2101,10 +2020,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="F2" s="27" t="s">
         <v>41</v>
@@ -2136,16 +2055,16 @@
         <v>2</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="F3" s="27" t="s">
         <v>45</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="H3" s="28" t="n">
         <v>35000</v>
@@ -2171,16 +2090,16 @@
         <v>3</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="F4" s="27" t="s">
         <v>45</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="H4" s="28" t="n">
         <v>32400</v>
@@ -2206,16 +2125,16 @@
         <v>4</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="F5" s="27" t="s">
         <v>45</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="H5" s="28" t="n">
         <v>25000</v>
@@ -2241,16 +2160,16 @@
         <v>5</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="H6" s="28" t="n">
         <v>5600</v>
@@ -2276,16 +2195,16 @@
         <v>6</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="H7" s="28" t="n">
         <v>72000</v>
@@ -2311,16 +2230,16 @@
         <v>19</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H8" s="28" t="n">
         <v>8000</v>
@@ -2346,16 +2265,16 @@
         <v>7</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="H9" s="28" t="n">
         <v>960</v>
@@ -2381,16 +2300,16 @@
         <v>8</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="H10" s="28" t="n">
         <v>2000</v>
@@ -2416,16 +2335,16 @@
         <v>17</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="H11" s="28" t="n">
         <v>5000</v>
@@ -2451,16 +2370,16 @@
         <v>18</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="H12" s="28" t="n">
         <v>2000</v>
@@ -2486,16 +2405,16 @@
         <v>9</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H13" s="28" t="n">
         <v>210000</v>
@@ -2521,16 +2440,16 @@
         <v>10</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="H14" s="28" t="n">
         <v>75000</v>
@@ -2556,16 +2475,16 @@
         <v>11</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="H15" s="28" t="n">
         <v>125000</v>
@@ -2591,16 +2510,16 @@
         <v>12</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F16" s="27" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="H16" s="28" t="n">
         <v>200000</v>
@@ -2626,16 +2545,16 @@
         <v>13</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="H17" s="28" t="n">
         <v>200000</v>
@@ -2661,16 +2580,16 @@
         <v>14</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F18" s="27" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H18" s="28" t="n">
         <v>180000</v>
@@ -2696,16 +2615,16 @@
         <v>15</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="H19" s="28" t="n">
         <v>30000</v>
@@ -2731,16 +2650,16 @@
         <v>16</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E20" s="26" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F20" s="27" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H20" s="28" t="n">
         <v>51200</v>
@@ -2757,25 +2676,25 @@
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C21" s="26" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="H21" s="28" t="n">
         <v>19152</v>
@@ -2792,25 +2711,25 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C22" s="26" t="n">
         <v>2</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F22" s="27" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H22" s="28" t="n">
         <v>2016</v>
@@ -2827,25 +2746,25 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="26" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C23" s="26" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F23" s="27" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H23" s="28" t="n">
         <v>33600</v>
@@ -2862,25 +2781,25 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="26" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C24" s="26" t="n">
         <v>2</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F24" s="27" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H24" s="28" t="n">
         <v>2160</v>
@@ -2897,25 +2816,25 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="26" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C25" s="26" t="n">
         <v>3</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H25" s="28" t="n">
         <v>8000</v>
@@ -2938,7 +2857,7 @@
       <c r="E26" s="20"/>
       <c r="F26" s="20"/>
       <c r="G26" s="21" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H26" s="22" t="n">
         <f aca="false">SUM(H2:H25)</f>
@@ -2975,7 +2894,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
@@ -2985,194 +2904,205 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="30" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C3" s="30" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>143</v>
-      </c>
-      <c r="B5" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="C9" s="7" t="s">
         <v>153</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="32" t="s">
-        <v>152</v>
-      </c>
-      <c r="B9" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B10" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>157</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="32" t="s">
-        <v>152</v>
-      </c>
-      <c r="B11" s="33" t="s">
-        <v>159</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="32" t="s">
+        <v>158</v>
+      </c>
+      <c r="B13" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="B13" s="33" t="s">
-        <v>164</v>
-      </c>
       <c r="C13" s="32" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="32" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="32" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="32" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>175</v>
-      </c>
       <c r="C18" s="7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="C20" s="7" t="s">
         <v>178</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -3191,7 +3121,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
@@ -3200,75 +3130,83 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B3" s="34" t="s">
         <v>181</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B4" s="35" t="s">
         <v>183</v>
-      </c>
-      <c r="B4" s="35" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B5" s="35" t="s">
         <v>185</v>
-      </c>
-      <c r="B5" s="35" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B6" s="35" t="s">
         <v>187</v>
-      </c>
-      <c r="B6" s="35" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B7" s="35" t="s">
         <v>189</v>
-      </c>
-      <c r="B7" s="35" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B8" s="35" t="s">
         <v>191</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B9" s="35" t="s">
         <v>193</v>
       </c>
-      <c r="B9" s="35" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
-      <c r="B10" s="35"/>
-    </row>
-    <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="36" t="s">
+      <c r="B10" s="35" t="s">
         <v>195</v>
       </c>
-      <c r="B11" s="37" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3"/>
+      <c r="B11" s="35"/>
+    </row>
+    <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="36" t="s">
         <v>196</v>
+      </c>
+      <c r="B12" s="37" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>

--- a/output/HS_Code_Summary_Sonavox_Technology_CZ_TECGO26080029.xlsx
+++ b/output/HS_Code_Summary_Sonavox_Technology_CZ_TECGO26080029.xlsx
@@ -26,9 +26,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="200">
   <si>
     <t xml:space="preserve">HS CODE SUMMARY – Sonavox Technology CZ s.r.o.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference MW:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CZ26011282 (Josef Šrejber – RAIL) | celní režim: volný oběh | celnice: A1 Ostrava | příjezd cca 34. týden</t>
   </si>
   <si>
     <t xml:space="preserve">Odesílatelé / Senders:</t>
@@ -1213,7 +1219,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
@@ -1315,10 +1321,10 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1331,581 +1337,573 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="6" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="B18" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="C18" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="D18" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="E18" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="F18" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I17" s="6" t="s">
+      <c r="G18" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="J17" s="6" t="s">
+      <c r="H18" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="K17" s="6" t="s">
+      <c r="I18" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="L17" s="6" t="s">
+      <c r="J18" s="6" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
+      <c r="K18" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="L18" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="8" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="B19" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E18" s="9" t="n">
-        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A18,'Line items'!$F$2:$F$25,$C18)</f>
-        <v>65000</v>
-      </c>
-      <c r="F18" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A18,'Line items'!$F$2:$F$25,$C18)</f>
-        <v>86.5</v>
-      </c>
-      <c r="G18" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A18,'Line items'!$F$2:$F$25,$C18)</f>
-        <v>216.33</v>
-      </c>
-      <c r="H18" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A18,'Line items'!$F$2:$F$25,$C18)</f>
-        <v>9841</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J18" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="K18" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="L18" s="7" t="s">
+      <c r="D19" s="7" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>46</v>
       </c>
       <c r="E19" s="9" t="n">
         <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A19,'Line items'!$F$2:$F$25,$C19)</f>
-        <v>778000</v>
+        <v>65000</v>
       </c>
       <c r="F19" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A19,'Line items'!$F$2:$F$25,$C19)</f>
-        <v>8806.4</v>
+        <v>86.5</v>
       </c>
       <c r="G19" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A19,'Line items'!$F$2:$F$25,$C19)</f>
-        <v>8990.91</v>
+        <v>216.33</v>
       </c>
       <c r="H19" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A19,'Line items'!$F$2:$F$25,$C19)</f>
-        <v>32182.14</v>
+        <v>9841</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L19" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="8" t="s">
+      <c r="D20" s="7" t="s">
         <v>48</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>49</v>
       </c>
       <c r="E20" s="9" t="n">
         <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A20,'Line items'!$F$2:$F$25,$C20)</f>
-        <v>9960</v>
+        <v>778000</v>
       </c>
       <c r="F20" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A20,'Line items'!$F$2:$F$25,$C20)</f>
-        <v>103.09</v>
+        <v>8806.4</v>
       </c>
       <c r="G20" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A20,'Line items'!$F$2:$F$25,$C20)</f>
-        <v>128</v>
+        <v>8990.91</v>
       </c>
       <c r="H20" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A20,'Line items'!$F$2:$F$25,$C20)</f>
-        <v>1378.1</v>
+        <v>32182.14</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C21" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>52</v>
       </c>
       <c r="E21" s="9" t="n">
         <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A21,'Line items'!$F$2:$F$25,$C21)</f>
-        <v>210000</v>
+        <v>9960</v>
       </c>
       <c r="F21" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A21,'Line items'!$F$2:$F$25,$C21)</f>
-        <v>30.24</v>
+        <v>103.09</v>
       </c>
       <c r="G21" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A21,'Line items'!$F$2:$F$25,$C21)</f>
-        <v>40</v>
+        <v>128</v>
       </c>
       <c r="H21" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A21,'Line items'!$F$2:$F$25,$C21)</f>
-        <v>8820</v>
+        <v>1378.1</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L21" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" s="12" t="s">
+      <c r="D22" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D22" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="E22" s="13" t="n">
+      <c r="E22" s="9" t="n">
         <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A22,'Line items'!$F$2:$F$25,$C22)</f>
         <v>210000</v>
       </c>
-      <c r="F22" s="14" t="n">
+      <c r="F22" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A22,'Line items'!$F$2:$F$25,$C22)</f>
+        <v>30.24</v>
+      </c>
+      <c r="G22" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A22,'Line items'!$F$2:$F$25,$C22)</f>
+        <v>40</v>
+      </c>
+      <c r="H22" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A22,'Line items'!$F$2:$F$25,$C22)</f>
+        <v>8820</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A23,'Line items'!$F$2:$F$25,$C23)</f>
+        <v>210000</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A23,'Line items'!$F$2:$F$25,$C23)</f>
         <v>312.3</v>
       </c>
-      <c r="G22" s="14" t="n">
-        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A22,'Line items'!$F$2:$F$25,$C22)</f>
+      <c r="G23" s="14" t="n">
+        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A23,'Line items'!$F$2:$F$25,$C23)</f>
         <v>325.5</v>
       </c>
-      <c r="H22" s="14" t="n">
-        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A22,'Line items'!$F$2:$F$25,$C22)</f>
+      <c r="H23" s="14" t="n">
+        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A23,'Line items'!$F$2:$F$25,$C23)</f>
         <v>13140</v>
       </c>
-      <c r="I22" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J22" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="K22" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="L22" s="11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="8" t="s">
+      <c r="I23" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="K23" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="L23" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="E23" s="9" t="n">
-        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A23,'Line items'!$F$2:$F$25,$C23)</f>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A24,'Line items'!$F$2:$F$25,$C24)</f>
         <v>51200</v>
       </c>
-      <c r="F23" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A23,'Line items'!$F$2:$F$25,$C23)</f>
+      <c r="F24" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A24,'Line items'!$F$2:$F$25,$C24)</f>
         <v>235.52</v>
       </c>
-      <c r="G23" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A23,'Line items'!$F$2:$F$25,$C23)</f>
+      <c r="G24" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A24,'Line items'!$F$2:$F$25,$C24)</f>
         <v>250</v>
       </c>
-      <c r="H23" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A23,'Line items'!$F$2:$F$25,$C23)</f>
+      <c r="H24" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A24,'Line items'!$F$2:$F$25,$C24)</f>
         <v>8120.32</v>
       </c>
-      <c r="I23" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="L23" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="16"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="E24" s="18" t="n">
-        <f aca="false">SUM(E18:E23)</f>
+      <c r="I24" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <f aca="false">SUM(E19:E24)</f>
         <v>1324160</v>
       </c>
-      <c r="F24" s="19" t="n">
-        <f aca="false">SUM(F18:F23)</f>
+      <c r="F25" s="19" t="n">
+        <f aca="false">SUM(F19:F24)</f>
         <v>9574.05</v>
       </c>
-      <c r="G24" s="19" t="n">
-        <f aca="false">SUM(G18:G23)</f>
+      <c r="G25" s="19" t="n">
+        <f aca="false">SUM(G19:G24)</f>
         <v>9950.74</v>
       </c>
-      <c r="H24" s="19" t="n">
-        <f aca="false">SUM(H18:H23)</f>
+      <c r="H25" s="19" t="n">
+        <f aca="false">SUM(H19:H24)</f>
         <v>73481.56</v>
       </c>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-    </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="E25" s="9" t="n">
-        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A25,'Line items'!$F$2:$F$25,$C25)</f>
-        <v>19152</v>
-      </c>
-      <c r="F25" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A25,'Line items'!$F$2:$F$25,$C25)</f>
-        <v>11299.68</v>
-      </c>
-      <c r="G25" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A25,'Line items'!$F$2:$F$25,$C25)</f>
-        <v>11688.8</v>
-      </c>
-      <c r="H25" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A25,'Line items'!$F$2:$F$25,$C25)</f>
-        <v>19918.08</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="L25" s="7" t="s">
-        <v>47</v>
-      </c>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>66</v>
       </c>
       <c r="E26" s="9" t="n">
         <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A26,'Line items'!$F$2:$F$25,$C26)</f>
-        <v>2016</v>
+        <v>19152</v>
       </c>
       <c r="F26" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A26,'Line items'!$F$2:$F$25,$C26)</f>
-        <v>1149.12</v>
+        <v>11299.68</v>
       </c>
       <c r="G26" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A26,'Line items'!$F$2:$F$25,$C26)</f>
-        <v>1219.04</v>
+        <v>11688.8</v>
       </c>
       <c r="H26" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A26,'Line items'!$F$2:$F$25,$C26)</f>
+        <v>19918.08</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A27,'Line items'!$F$2:$F$25,$C27)</f>
+        <v>2016</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A27,'Line items'!$F$2:$F$25,$C27)</f>
+        <v>1149.12</v>
+      </c>
+      <c r="G27" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A27,'Line items'!$F$2:$F$25,$C27)</f>
+        <v>1219.04</v>
+      </c>
+      <c r="H27" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A27,'Line items'!$F$2:$F$25,$C27)</f>
         <v>5140.8</v>
       </c>
-      <c r="I26" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="L26" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="16"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E27" s="18" t="n">
-        <f aca="false">SUM(E25:E26)</f>
+      <c r="I27" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <f aca="false">SUM(E26:E27)</f>
         <v>21168</v>
       </c>
-      <c r="F27" s="19" t="n">
-        <f aca="false">SUM(F25:F26)</f>
+      <c r="F28" s="19" t="n">
+        <f aca="false">SUM(F26:F27)</f>
         <v>12448.8</v>
       </c>
-      <c r="G27" s="19" t="n">
-        <f aca="false">SUM(G25:G26)</f>
+      <c r="G28" s="19" t="n">
+        <f aca="false">SUM(G26:G27)</f>
         <v>12907.84</v>
       </c>
-      <c r="H27" s="19" t="n">
-        <f aca="false">SUM(H25:H26)</f>
+      <c r="H28" s="19" t="n">
+        <f aca="false">SUM(H26:H27)</f>
         <v>25058.88</v>
       </c>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-    </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="8" t="s">
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A29,'Line items'!$F$2:$F$25,$C29)</f>
+        <v>43760</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A29,'Line items'!$F$2:$F$25,$C29)</f>
+        <v>957</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A29,'Line items'!$F$2:$F$25,$C29)</f>
+        <v>1274.42</v>
+      </c>
+      <c r="H29" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A29,'Line items'!$F$2:$F$25,$C29)</f>
+        <v>20830.64</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J29" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D28" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E28" s="9" t="n">
-        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A28,'Line items'!$F$2:$F$25,$C28)</f>
+      <c r="K29" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="16"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="E30" s="18" t="n">
+        <f aca="false">SUM(E29:E29)</f>
         <v>43760</v>
       </c>
-      <c r="F28" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A28,'Line items'!$F$2:$F$25,$C28)</f>
+      <c r="F30" s="19" t="n">
+        <f aca="false">SUM(F29:F29)</f>
         <v>957</v>
       </c>
-      <c r="G28" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A28,'Line items'!$F$2:$F$25,$C28)</f>
+      <c r="G30" s="19" t="n">
+        <f aca="false">SUM(G29:G29)</f>
         <v>1274.42</v>
       </c>
-      <c r="H28" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A28,'Line items'!$F$2:$F$25,$C28)</f>
+      <c r="H30" s="19" t="n">
+        <f aca="false">SUM(H29:H29)</f>
         <v>20830.64</v>
       </c>
-      <c r="I28" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K28" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="L28" s="7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="16"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E29" s="18" t="n">
-        <f aca="false">SUM(E28:E28)</f>
-        <v>43760</v>
-      </c>
-      <c r="F29" s="19" t="n">
-        <f aca="false">SUM(F28:F28)</f>
-        <v>957</v>
-      </c>
-      <c r="G29" s="19" t="n">
-        <f aca="false">SUM(G28:G28)</f>
-        <v>1274.42</v>
-      </c>
-      <c r="H29" s="19" t="n">
-        <f aca="false">SUM(H28:H28)</f>
-        <v>20830.64</v>
-      </c>
-      <c r="I29" s="16"/>
-      <c r="J29" s="16"/>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="20"/>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="E30" s="22" t="n">
-        <f aca="false">E24+E27+E29</f>
+      <c r="I30" s="16"/>
+      <c r="J30" s="16"/>
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="20"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E31" s="22" t="n">
+        <f aca="false">E25+E28+E30</f>
         <v>1389088</v>
       </c>
-      <c r="F30" s="23" t="n">
-        <f aca="false">F24+F27+F29</f>
+      <c r="F31" s="23" t="n">
+        <f aca="false">F25+F28+F30</f>
         <v>22979.85</v>
       </c>
-      <c r="G30" s="23" t="n">
-        <f aca="false">G24+G27+G29</f>
+      <c r="G31" s="23" t="n">
+        <f aca="false">G25+G28+G30</f>
         <v>24133</v>
       </c>
-      <c r="H30" s="23" t="n">
-        <f aca="false">H24+H27+H29</f>
+      <c r="H31" s="23" t="n">
+        <f aca="false">H25+H28+H30</f>
         <v>119371.08</v>
       </c>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C32" s="2" t="s">
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="B33" s="2" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
+      <c r="C33" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B33" s="24" t="n">
-        <f aca="false">E30</f>
-        <v>1389088</v>
-      </c>
-      <c r="C33" s="24" t="n">
-        <v>1389088</v>
-      </c>
-      <c r="D33" s="24" t="n">
-        <f aca="false">B33-C33</f>
-        <v>0</v>
+      <c r="D33" s="2" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B34" s="24" t="n">
-        <f aca="false">F30</f>
-        <v>22979.85</v>
+        <f aca="false">E31</f>
+        <v>1389088</v>
       </c>
       <c r="C34" s="24" t="n">
-        <v>22979.85</v>
+        <v>1389088</v>
       </c>
       <c r="D34" s="24" t="n">
         <f aca="false">B34-C34</f>
@@ -1914,14 +1912,14 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B35" s="24" t="n">
-        <f aca="false">G30</f>
-        <v>24133</v>
+        <f aca="false">F31</f>
+        <v>22979.85</v>
       </c>
       <c r="C35" s="24" t="n">
-        <v>24133</v>
+        <v>22979.85</v>
       </c>
       <c r="D35" s="24" t="n">
         <f aca="false">B35-C35</f>
@@ -1930,17 +1928,33 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B36" s="24" t="n">
-        <f aca="false">H30</f>
-        <v>119371.08</v>
+        <f aca="false">G31</f>
+        <v>24133</v>
       </c>
       <c r="C36" s="24" t="n">
-        <v>119371.08</v>
+        <v>24133</v>
       </c>
       <c r="D36" s="24" t="n">
         <f aca="false">B36-C36</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" s="24" t="n">
+        <f aca="false">H31</f>
+        <v>119371.08</v>
+      </c>
+      <c r="C37" s="24" t="n">
+        <v>119371.08</v>
+      </c>
+      <c r="D37" s="24" t="n">
+        <f aca="false">B37-C37</f>
         <v>0</v>
       </c>
     </row>
@@ -1976,60 +1990,60 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E1" s="25" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F1" s="25" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G1" s="25" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H1" s="25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I1" s="25" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J1" s="25" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K1" s="25" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C2" s="26" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H2" s="28" t="n">
         <v>65000</v>
@@ -2046,25 +2060,25 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C3" s="26" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F3" s="27" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H3" s="28" t="n">
         <v>35000</v>
@@ -2081,25 +2095,25 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C4" s="26" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="E4" s="26" t="s">
-        <v>95</v>
-      </c>
       <c r="F4" s="27" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H4" s="28" t="n">
         <v>32400</v>
@@ -2116,25 +2130,25 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C5" s="26" t="n">
         <v>4</v>
       </c>
       <c r="D5" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="F5" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>98</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="F5" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>96</v>
       </c>
       <c r="H5" s="28" t="n">
         <v>25000</v>
@@ -2151,25 +2165,25 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C6" s="26" t="n">
         <v>5</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H6" s="28" t="n">
         <v>5600</v>
@@ -2186,25 +2200,25 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C7" s="26" t="n">
         <v>6</v>
       </c>
       <c r="D7" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="E7" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="E7" s="26" t="s">
-        <v>100</v>
-      </c>
       <c r="F7" s="27" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H7" s="28" t="n">
         <v>72000</v>
@@ -2221,25 +2235,25 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C8" s="26" t="n">
         <v>19</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H8" s="28" t="n">
         <v>8000</v>
@@ -2256,25 +2270,25 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C9" s="26" t="n">
         <v>7</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H9" s="28" t="n">
         <v>960</v>
@@ -2291,25 +2305,25 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C10" s="26" t="n">
         <v>8</v>
       </c>
       <c r="D10" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="E10" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="E10" s="26" t="s">
-        <v>106</v>
-      </c>
       <c r="F10" s="27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H10" s="28" t="n">
         <v>2000</v>
@@ -2326,25 +2340,25 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C11" s="26" t="n">
         <v>17</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H11" s="28" t="n">
         <v>5000</v>
@@ -2361,25 +2375,25 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C12" s="26" t="n">
         <v>18</v>
       </c>
       <c r="D12" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="E12" s="26" t="s">
-        <v>110</v>
-      </c>
       <c r="F12" s="27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H12" s="28" t="n">
         <v>2000</v>
@@ -2396,25 +2410,25 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C13" s="26" t="n">
         <v>9</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H13" s="28" t="n">
         <v>210000</v>
@@ -2431,25 +2445,25 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C14" s="26" t="n">
         <v>10</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H14" s="28" t="n">
         <v>75000</v>
@@ -2466,25 +2480,25 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C15" s="26" t="n">
         <v>11</v>
       </c>
       <c r="D15" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="E15" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="E15" s="26" t="s">
-        <v>116</v>
-      </c>
       <c r="F15" s="27" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H15" s="28" t="n">
         <v>125000</v>
@@ -2501,25 +2515,25 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C16" s="26" t="n">
         <v>12</v>
       </c>
       <c r="D16" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="F16" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="7" t="s">
         <v>119</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="F16" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>117</v>
       </c>
       <c r="H16" s="28" t="n">
         <v>200000</v>
@@ -2536,25 +2550,25 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C17" s="26" t="n">
         <v>13</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H17" s="28" t="n">
         <v>200000</v>
@@ -2571,25 +2585,25 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C18" s="26" t="n">
         <v>14</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F18" s="27" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H18" s="28" t="n">
         <v>180000</v>
@@ -2606,25 +2620,25 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C19" s="26" t="n">
         <v>15</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H19" s="28" t="n">
         <v>30000</v>
@@ -2641,25 +2655,25 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C20" s="26" t="n">
         <v>16</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E20" s="26" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F20" s="27" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H20" s="28" t="n">
         <v>51200</v>
@@ -2676,25 +2690,25 @@
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C21" s="26" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H21" s="28" t="n">
         <v>19152</v>
@@ -2711,25 +2725,25 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C22" s="26" t="n">
         <v>2</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F22" s="27" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H22" s="28" t="n">
         <v>2016</v>
@@ -2746,25 +2760,25 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="26" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C23" s="26" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F23" s="27" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H23" s="28" t="n">
         <v>33600</v>
@@ -2781,25 +2795,25 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="26" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C24" s="26" t="n">
         <v>2</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F24" s="27" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H24" s="28" t="n">
         <v>2160</v>
@@ -2816,25 +2830,25 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="26" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C25" s="26" t="n">
         <v>3</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H25" s="28" t="n">
         <v>8000</v>
@@ -2857,7 +2871,7 @@
       <c r="E26" s="20"/>
       <c r="F26" s="20"/>
       <c r="G26" s="21" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H26" s="22" t="n">
         <f aca="false">SUM(H2:H25)</f>
@@ -2904,205 +2918,205 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C3" s="30" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="32" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="32" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="32" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="32" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -3130,71 +3144,71 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3203,10 +3217,10 @@
     </row>
     <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="36" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/output/HS_Code_Summary_Sonavox_Technology_CZ_TECGO26080029.xlsx
+++ b/output/HS_Code_Summary_Sonavox_Technology_CZ_TECGO26080029.xlsx
@@ -205,7 +205,10 @@
     <t xml:space="preserve">ANO</t>
   </si>
   <si>
-    <t xml:space="preserve">Spojovací materiál ze železa/oceli, původ ČÍNA – viz list Poznámky.</t>
+    <t xml:space="preserve">K OVĚŘENÍ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spojovací materiál ze železa/oceli, původ ČÍNA. CBAM platí vždy (i pro hliníkovou variantu 7616). Antidumping závisí na tom, zda jde o matici (7318 16 – mimo působnost) nebo šroub/vložku (ex 7318 15 95 – AD 22,1–86,5 %). Viz list Poznámky.</t>
   </si>
   <si>
     <t xml:space="preserve">7413000090</t>
@@ -466,25 +469,22 @@
     <t xml:space="preserve">Všechny tři faktury i packing listy uvádějí pouze „Terms of Payment: FOB“ – BEZ uvedení přístavu / jmenovaného místa. Dvojí problém: (1) dle standardu musí být vždy uveden termín i město (např. FCA Suzhou); (2) FOB je dle Incoterms 2020 určen výhradně pro námořní a vnitrozemskou vodní přepravu, ale tato zásilka jde ŽELEZNICÍ (Zhengzhou/Putian → Malaszewicze → CZ). Pro železniční přepravu je správný termín FCA s uvedeným místem. Nutno vyžádat od odesílatele opravu / doplnění, jinak nelze spolehlivě určit, zda je do celní hodnoty nutno připočíst dopravné do hranice EU.</t>
   </si>
   <si>
-    <t xml:space="preserve">Antidumping – spojovací materiál ze železa/oceli (HS 7318), původ Čína</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Položky 14 (Nut, 029-2513-AL-CZ) a 15 (Spring nut, 029A-000004-CZ) od odesílatele Suzhou Sonavox International Trading, zařazené pod 7318 15 95, spadají do rozsahu platných antidumpingových opatření EU na spojovací prostředky ze železa nebo oceli pocházející z ČLR (nař. (EU) 2022/191 ve znění pozdějších předpisů, včetně opatření proti obcházení). Celní hodnota těchto položek: 13 140,00 EUR. Nutno ověřit doplňkový kód TARIC podle konkrétního čínského výrobce – sazba se dle výrobce významně liší.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CBAM – spojovací materiál ze železa/oceli (HS 7318)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tytéž položky pod kódem 7318 15 95 spadají do přílohy I nařízení CBAM (železo a ocel). Celkem 210 000 ks, čistá hmotnost 312,30 kg. Nutno zahrnout do čtvrtletního CBAM hlášení (vykazuje se čistá hmotnost a zabudované emise). Ostatní položky zásilky (kap. 35, 39, 74, 85) do CBAM nespadají.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K OVĚŘENÍ</t>
+    <t xml:space="preserve">Antidumping – závisí na materiálu A na tom, čím díl skutečně je</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Položky 14 (Nut, 029-2513-AL-CZ) a 15 (Spring nut, 029A-000004-CZ), celkem 13 140,00 EUR, mají tři možné scénáře: (a) HLINÍK → 7616 10 00, clo cca 6 %, BEZ antidumpingu; (b) OCELOVÁ MATICE → 7318 16, clo cca 3,7 %, BEZ antidumpingu; (c) OCELOVÝ ŠROUB / ZÁVITOVÁ VLOŽKA → ex 7318 15 95, clo 3,7 % + ANTIDUMPING 22,1–86,5 %. Nař. (EU) 2022/191 se vztahuje na vruty, samořezné šrouby, ostatní šrouby a svorníky s hlavou a podložky (kódy 7318 12 90, 7318 14 91, 7318 14 99, 7318 15 58, 7318 15 68, 7318 15 82, 7318 15 88, ex 7318 15 95, ex 7318 21 00, ex 7318 22 00) – kód 7318 16 pro MATICE v seznamu NENÍ, samostatné matice tedy do působnosti nespadají. Tabulka SONAVOX přiřazuje „Insert (nut)“ kód 7318 15 95 19, tj. kód pro šrouby, což u dílu nazvaného „nut“ může být chybné. V souhrnu je konzervativně ponecháno 7318 15 95 19. NUTNO ZJISTIT MATERIÁL I SKUTEČNÝ DRUH DÍLU; při variantě (c) je nutný doplňkový kód TARIC dle výrobce – bez jména výrobce se uplatní zbytková sazba 86,5 %.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBAM – platí u matic v každé variantě</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Položky 14 a 15 (210 000 ks, čistá hmotnost 312,30 kg) spadají do přílohy I nařízení CBAM bez ohledu na to, jak dopadne otázka materiálu: kapitola 73 (železo a ocel) i kapitola 76 (hliník) jsou v příloze I. Nutno zahrnout do čtvrtletního CBAM hlášení (vykazuje se čistá hmotnost a zabudované emise). Ostatní položky zásilky (kap. 35, 39, 85) do CBAM nespadají.</t>
   </si>
   <si>
     <t xml:space="preserve">Nesoulad: „Nut 029-2513-AL-CZ“ – ocel nebo hliník?</t>
   </si>
   <si>
-    <t xml:space="preserve">Označení dílu obsahuje „-AL-“, což naznačuje HLINÍK, avšak podklad SONAVOX (e-mail „SONAVOX HS KODY“) přiřazuje „Insert (nut)“ kód 7318 15 95 19 (železo/ocel). Hliníková matice by patřila pod 7616 10 00. Zařazení má přímý dopad: 7318 = antidumping ANO + CBAM ANO; 7616 = antidumping NE + CBAM ANO. V souhrnu je konzervativně použito 7318 15 95 19. NUTNO POTVRDIT MATERIÁL U DODAVATELE.</t>
+    <t xml:space="preserve">Označení dílu obsahuje „-AL-“, což naznačuje HLINÍK, avšak podklad SONAVOX (e-mail „SONAVOX HS KODY“) přiřazuje „Insert (nut)“ kód 7318 15 95 19 (železo/ocel). Hliníková matice by patřila pod 7616 10 00. Zařazení má přímý dopad: 7318 = antidumping ANO + CBAM ANO; 7616 = antidumping NE + CBAM ANO. V souhrnu je konzervativně použito 7318 15 95 19. NUTNO POTVRDIT MATERIÁL I DRUH DÍLU U DODAVATELE (matice vs. závitová vložka/šroub) – viz poznámka k antidumpingu.</t>
   </si>
   <si>
     <t xml:space="preserve">VYŘEŠENO</t>
@@ -1558,7 +1558,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
         <v>41</v>
       </c>
@@ -1594,10 +1594,10 @@
         <v>58</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1608,10 +1608,10 @@
         <v>42</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E24" s="9" t="n">
         <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A24,'Line items'!$F$2:$F$25,$C24)</f>
@@ -1639,7 +1639,7 @@
         <v>45</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1647,7 +1647,7 @@
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
       <c r="D25" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E25" s="18" t="n">
         <f aca="false">SUM(E19:E24)</f>
@@ -1672,16 +1672,16 @@
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>47</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E26" s="9" t="n">
         <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A26,'Line items'!$F$2:$F$25,$C26)</f>
@@ -1714,16 +1714,16 @@
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E27" s="9" t="n">
         <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A27,'Line items'!$F$2:$F$25,$C27)</f>
@@ -1751,7 +1751,7 @@
         <v>45</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1759,7 +1759,7 @@
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
       <c r="D28" s="17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E28" s="18" t="n">
         <f aca="false">SUM(E26:E27)</f>
@@ -1784,16 +1784,16 @@
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>47</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E29" s="9" t="n">
         <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A29,'Line items'!$F$2:$F$25,$C29)</f>
@@ -1829,7 +1829,7 @@
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
       <c r="D30" s="17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E30" s="18" t="n">
         <f aca="false">SUM(E29:E29)</f>
@@ -1857,7 +1857,7 @@
       <c r="B31" s="20"/>
       <c r="C31" s="20"/>
       <c r="D31" s="21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E31" s="22" t="n">
         <f aca="false">E25+E28+E30</f>
@@ -1882,21 +1882,21 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B34" s="24" t="n">
         <f aca="false">E31</f>
@@ -1912,7 +1912,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B35" s="24" t="n">
         <f aca="false">F31</f>
@@ -1928,7 +1928,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B36" s="24" t="n">
         <f aca="false">G31</f>
@@ -1944,7 +1944,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B37" s="24" t="n">
         <f aca="false">H31</f>
@@ -1990,37 +1990,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E1" s="25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F1" s="25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G1" s="25" t="s">
         <v>32</v>
       </c>
       <c r="H1" s="25" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I1" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J1" s="25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K1" s="25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2034,10 +2034,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F2" s="27" t="s">
         <v>43</v>
@@ -2069,16 +2069,16 @@
         <v>2</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F3" s="27" t="s">
         <v>47</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H3" s="28" t="n">
         <v>35000</v>
@@ -2104,16 +2104,16 @@
         <v>3</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F4" s="27" t="s">
         <v>47</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H4" s="28" t="n">
         <v>32400</v>
@@ -2139,16 +2139,16 @@
         <v>4</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F5" s="27" t="s">
         <v>47</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H5" s="28" t="n">
         <v>25000</v>
@@ -2174,16 +2174,16 @@
         <v>5</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F6" s="27" t="s">
         <v>47</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H6" s="28" t="n">
         <v>5600</v>
@@ -2209,16 +2209,16 @@
         <v>6</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F7" s="27" t="s">
         <v>47</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H7" s="28" t="n">
         <v>72000</v>
@@ -2244,16 +2244,16 @@
         <v>19</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F8" s="27" t="s">
         <v>47</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H8" s="28" t="n">
         <v>8000</v>
@@ -2279,16 +2279,16 @@
         <v>7</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F9" s="27" t="s">
         <v>50</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H9" s="28" t="n">
         <v>960</v>
@@ -2314,16 +2314,16 @@
         <v>8</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F10" s="27" t="s">
         <v>50</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H10" s="28" t="n">
         <v>2000</v>
@@ -2349,16 +2349,16 @@
         <v>17</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F11" s="27" t="s">
         <v>50</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H11" s="28" t="n">
         <v>5000</v>
@@ -2384,16 +2384,16 @@
         <v>18</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F12" s="27" t="s">
         <v>50</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H12" s="28" t="n">
         <v>2000</v>
@@ -2419,10 +2419,10 @@
         <v>9</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F13" s="27" t="s">
         <v>53</v>
@@ -2454,16 +2454,16 @@
         <v>10</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F14" s="27" t="s">
         <v>47</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H14" s="28" t="n">
         <v>75000</v>
@@ -2489,16 +2489,16 @@
         <v>11</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>47</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H15" s="28" t="n">
         <v>125000</v>
@@ -2524,16 +2524,16 @@
         <v>12</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F16" s="27" t="s">
         <v>47</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H16" s="28" t="n">
         <v>200000</v>
@@ -2559,16 +2559,16 @@
         <v>13</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F17" s="27" t="s">
         <v>47</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H17" s="28" t="n">
         <v>200000</v>
@@ -2594,10 +2594,10 @@
         <v>14</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F18" s="27" t="s">
         <v>56</v>
@@ -2629,10 +2629,10 @@
         <v>15</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F19" s="27" t="s">
         <v>56</v>
@@ -2664,16 +2664,16 @@
         <v>16</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E20" s="26" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F20" s="27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H20" s="28" t="n">
         <v>51200</v>
@@ -2690,25 +2690,25 @@
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C21" s="26" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F21" s="27" t="s">
         <v>47</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H21" s="28" t="n">
         <v>19152</v>
@@ -2725,25 +2725,25 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C22" s="26" t="n">
         <v>2</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F22" s="27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H22" s="28" t="n">
         <v>2016</v>
@@ -2760,25 +2760,25 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C23" s="26" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F23" s="27" t="s">
         <v>47</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H23" s="28" t="n">
         <v>33600</v>
@@ -2795,25 +2795,25 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C24" s="26" t="n">
         <v>2</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F24" s="27" t="s">
         <v>47</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H24" s="28" t="n">
         <v>2160</v>
@@ -2830,25 +2830,25 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C25" s="26" t="n">
         <v>3</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F25" s="27" t="s">
         <v>47</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H25" s="28" t="n">
         <v>8000</v>
@@ -2871,7 +2871,7 @@
       <c r="E26" s="20"/>
       <c r="F26" s="20"/>
       <c r="G26" s="21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H26" s="22" t="n">
         <f aca="false">SUM(H2:H25)</f>
@@ -2918,67 +2918,67 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="30" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C3" s="30" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="32" t="s">
-        <v>150</v>
+        <v>59</v>
       </c>
       <c r="B8" s="33" t="s">
         <v>151</v>
@@ -3000,7 +3000,7 @@
     </row>
     <row r="10" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>150</v>
+        <v>59</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>156</v>

--- a/output/HS_Code_Summary_Sonavox_Technology_CZ_TECGO26080029.xlsx
+++ b/output/HS_Code_Summary_Sonavox_Technology_CZ_TECGO26080029.xlsx
@@ -5,16 +5,17 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="HS Summary" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Line items" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Poznámky &amp; flagy" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Zdroje" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Chybějící HS kódy" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Line items" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Poznámky &amp; flagy" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Zdroje" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Line items'!$A$1:$K$25</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Line items'!$A$1:$L$25</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="221">
   <si>
     <t xml:space="preserve">HS CODE SUMMARY – Sonavox Technology CZ s.r.o.</t>
   </si>
@@ -34,13 +35,13 @@
     <t xml:space="preserve">Reference MW:</t>
   </si>
   <si>
-    <t xml:space="preserve">CZ26011282 (Josef Šrejber – RAIL) | celní režim: volný oběh | celnice: A1 Ostrava | příjezd cca 34. týden</t>
+    <t xml:space="preserve">CZ26011282 (Josef Šrejber – RAIL) | režim: volný oběh | celnice: A1 Ostrava | příjezd cca 34. týden</t>
   </si>
   <si>
     <t xml:space="preserve">Odesílatelé / Senders:</t>
   </si>
   <si>
-    <t xml:space="preserve">3 (viz členění níže) – zásilka je členěna PRIMÁRNĚ dle odesílatele</t>
+    <t xml:space="preserve">3 – zásilka je členěna PRIMÁRNĚ dle odesílatele</t>
   </si>
   <si>
     <t xml:space="preserve">Příjemce / Consignee:</t>
@@ -85,12 +86,6 @@
     <t xml:space="preserve">Čína (Suzhou, 35029)</t>
   </si>
   <si>
-    <t xml:space="preserve">Destinace:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czech Republic / EU</t>
-  </si>
-  <si>
     <t xml:space="preserve">Měna:</t>
   </si>
   <si>
@@ -106,7 +101,7 @@
     <t xml:space="preserve">Preferenční věta:</t>
   </si>
   <si>
-    <t xml:space="preserve">NENALEZENA v žádném dokladu – viz list Poznámky (kritické)</t>
+    <t xml:space="preserve">NENALEZENA v žádném dokladu – viz list Poznámky</t>
   </si>
   <si>
     <t xml:space="preserve">Celkem kolí / objem:</t>
@@ -115,6 +110,12 @@
     <t xml:space="preserve">51 palet / 51,40 CBM / brutto 24 133 kg (souhlasí s FCR i SMGS)</t>
   </si>
   <si>
+    <t xml:space="preserve">CHYBĚJÍCÍ HS KÓDY:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 položky bez kódu v podkladech (9 360,00 EUR) – viz list „Chybějící HS kódy“</t>
+  </si>
+  <si>
     <t xml:space="preserve">Odesílatel / Sender</t>
   </si>
   <si>
@@ -148,7 +149,7 @@
     <t xml:space="preserve">Antidumping</t>
   </si>
   <si>
-    <t xml:space="preserve">Poznámka</t>
+    <t xml:space="preserve">Zdroj HS kódu / poznámka</t>
   </si>
   <si>
     <t xml:space="preserve">Suzhou Sonavox International Trading Co., Ltd</t>
@@ -166,7 +167,7 @@
     <t xml:space="preserve">Ne</t>
   </si>
   <si>
-    <t xml:space="preserve">Zařazení dle ZISZ 30-0292-2016 (kmitací cívka = ostatní tlumivky).</t>
+    <t xml:space="preserve">Zařazení podloženo závaznou informací ZISZ 30-0292-2016.</t>
   </si>
   <si>
     <t xml:space="preserve">8518900000</t>
@@ -175,7 +176,7 @@
     <t xml:space="preserve">Ocelová deska (front plate) – součást autoreproduktoru; Středící membrána (spider) – naimpregnovaná textilie, součást autoreproduktoru; Membrána s vlnkou (cone) – membrána elektrodynamického reproduktoru; Kontakt / vývod (terminal) – část autoreproduktoru</t>
   </si>
   <si>
-    <t xml:space="preserve">Části a součásti reproduktorů. Přípona DK 00 a zařazení terminalu i front plate pod tento kód dle předchozího celního prohlášení Sonavox (viz list Zdroje).</t>
+    <t xml:space="preserve">Části a součásti reproduktorů, DK 00 dle předchozích celních prohlášení.</t>
   </si>
   <si>
     <t xml:space="preserve">3926909790</t>
@@ -184,16 +185,7 @@
     <t xml:space="preserve">Plastové těsnění (gasket) – ostatní výrobky z plastů; Plastový kalibr (gauge) – montážní přípravek, ostatní výrobky z plastů</t>
   </si>
   <si>
-    <t xml:space="preserve">Ostatní výrobky z plastů. Gasket + Gauge na jednom řádku, DK 90 – potvrzeno předchozím celním prohlášením Sonavox.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3921909090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plastová membrána (vodotěsná membrána) – ochranná membrána reproduktoru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ostatní desky, listy, fólie a pásy z plastů.</t>
+    <t xml:space="preserve">Ostatní výrobky z plastů, DK 90 dle předchozího celního prohlášení.</t>
   </si>
   <si>
     <t xml:space="preserve">7318159519</t>
@@ -208,16 +200,28 @@
     <t xml:space="preserve">K OVĚŘENÍ</t>
   </si>
   <si>
-    <t xml:space="preserve">Spojovací materiál ze železa/oceli, původ ČÍNA. CBAM platí vždy (i pro hliníkovou variantu 7616). Antidumping závisí na tom, zda jde o matici (7318 16 – mimo působnost) nebo šroub/vložku (ex 7318 15 95 – AD 22,1–86,5 %). Viz list Poznámky.</t>
+    <t xml:space="preserve">CBAM platí i pro hliníkovou variantu (7616). Antidumping závisí na materiálu a druhu dílu – viz list Poznámky.</t>
   </si>
   <si>
     <t xml:space="preserve">7413000090</t>
   </si>
   <si>
-    <t xml:space="preserve">Kabelový svazek – splétané lanko, slitina měď (78 %) a cín, neizolované</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Splétaná lanka z mědi, neizolovaná.</t>
+    <t xml:space="preserve">Kabelový svazek – splétaná lanka z mědi, elektricky neizolovaná</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Splétaná lanka z mědi, neizolovaná, DK 90 dle předchozího celního prohlášení.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHYBÍ – VYŽÁDAT OD KLIENTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vodotěsná membrána (dle faktury „Waterproof membrane“ – český popis není k dispozici)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NENÍ V PODKLADECH – v e-mailu SONAVOX ani v předchozích celních prohlášeních tato položka není</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pružná matice (dle faktury „Spring nut“ – český popis není k dispozici)</t>
   </si>
   <si>
     <t xml:space="preserve">Mezisoučet – Suzhou Sonavox International Trading Co., Ltd</t>
@@ -283,6 +287,48 @@
     <t xml:space="preserve">Celní hodnota celkem (EUR) vs. součet faktur</t>
   </si>
   <si>
+    <t xml:space="preserve">POLOŽKY BEZ HS KÓDU – NUTNO VYŽÁDAT OD KLIENTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyto položky nemají HS kód v žádném podkladu – ani v e-mailu „SONAVOX HS KODY“, ani v předchozích celních prohlášeních Sonavox. Kód nelze doplnit vlastním odvozením; musí ho poskytnout klient.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Odesílatel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pol. č.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Popis dle faktury (EN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Čistá hm. (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hrubá hm. (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS kód – DOPLNÍ KLIENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J2-10X002-0001-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterproof membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">029A-000004-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spring nut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CELKEM</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sender</t>
   </si>
   <si>
@@ -292,15 +338,9 @@
     <t xml:space="preserve">Item</t>
   </si>
   <si>
-    <t xml:space="preserve">Part Number</t>
-  </si>
-  <si>
     <t xml:space="preserve">Description of Goods (EN)</t>
   </si>
   <si>
-    <t xml:space="preserve">HS code</t>
-  </si>
-  <si>
     <t xml:space="preserve">Quantity (pcs)</t>
   </si>
   <si>
@@ -313,12 +353,18 @@
     <t xml:space="preserve">Customs value (EUR)</t>
   </si>
   <si>
+    <t xml:space="preserve">Zdroj HS kódu</t>
+  </si>
+  <si>
     <t xml:space="preserve">010-KD1622S-3.8A-CZ</t>
   </si>
   <si>
     <t xml:space="preserve">Voice coil</t>
   </si>
   <si>
+    <t xml:space="preserve">e-mail SONAVOX HS KODY: „Voice Coil / Kmitací cívka – HS 85045000 00“ (ZISZ 30-0292-2016)</t>
+  </si>
+  <si>
     <t xml:space="preserve">040-62E4-CR-CZ</t>
   </si>
   <si>
@@ -328,6 +374,9 @@
     <t xml:space="preserve">Ocelová deska (front plate) – součást autoreproduktoru</t>
   </si>
   <si>
+    <t xml:space="preserve">předchozí celní prohlášení Sonavox: „Front plate – deska“, CN 8518 90 00 DK 00 (POZOR: e-mail uvádí ...90 – rozpor)</t>
+  </si>
+  <si>
     <t xml:space="preserve">040-80I6-CRB-CZ</t>
   </si>
   <si>
@@ -343,6 +392,9 @@
     <t xml:space="preserve">Středící membrána (spider) – naimpregnovaná textilie, součást autoreproduktoru</t>
   </si>
   <si>
+    <t xml:space="preserve">e-mail SONAVOX HS KODY + předchozí celní prohlášení: „Spider – 8518 9000 00“</t>
+  </si>
+  <si>
     <t xml:space="preserve">021-80E15-3-CZ</t>
   </si>
   <si>
@@ -352,6 +404,30 @@
     <t xml:space="preserve">Cone</t>
   </si>
   <si>
+    <t xml:space="preserve">e-mail SONAVOX HS KODY + předchozí celní prohlášení: „Cone – HS 85189000 00“</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181-35113-1SN-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kontakt / vývod (terminal) – část autoreproduktoru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">předchozí celní prohlášení Sonavox: „terminal – části reproduktorů“, CN 8518 90 00 DK 00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181-35113-2SN-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181-40133-1SN-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181-40133-2SN-CZ</t>
+  </si>
+  <si>
     <t xml:space="preserve">142-630H10-15H-CZ</t>
   </si>
   <si>
@@ -361,6 +437,9 @@
     <t xml:space="preserve">Plastové těsnění (gasket) – ostatní výrobky z plastů</t>
   </si>
   <si>
+    <t xml:space="preserve">předchozí celní prohlášení Sonavox: „Gassket – plastové těsnění“, CN 3926 90 97 DK 90</t>
+  </si>
+  <si>
     <t xml:space="preserve">142-40X25-25D-CZ</t>
   </si>
   <si>
@@ -373,43 +452,19 @@
     <t xml:space="preserve">Plastový kalibr (gauge) – montážní přípravek, ostatní výrobky z plastů</t>
   </si>
   <si>
+    <t xml:space="preserve">e-mail SONAVOX HS KODY + předchozí celní prohlášení: „Gauge – 3926 9097 90“</t>
+  </si>
+  <si>
     <t xml:space="preserve">JK-35113-01-CZ</t>
   </si>
   <si>
-    <t xml:space="preserve">J2-10X002-0001-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterproof membrane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181-35113-1SN-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terminal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kontakt / vývod (terminal) – část autoreproduktoru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181-35113-2SN-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181-40133-1SN-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181-40133-2SN-CZ</t>
-  </si>
-  <si>
     <t xml:space="preserve">029-2513-AL-CZ</t>
   </si>
   <si>
     <t xml:space="preserve">Nut</t>
   </si>
   <si>
-    <t xml:space="preserve">029A-000004-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spring nut</t>
+    <t xml:space="preserve">e-mail SONAVOX HS KODY: „Insert (nut) – 7318159519“ (POZOR: materiál dílu neověřen – viz Poznámky)</t>
   </si>
   <si>
     <t xml:space="preserve">008-XH-2Y-DK-6-CZ</t>
@@ -418,18 +473,27 @@
     <t xml:space="preserve">Harness</t>
   </si>
   <si>
+    <t xml:space="preserve">předchozí celní prohlášení Sonavox: „harness – kabelový svazek“, CN 7413 00 00 DK 90</t>
+  </si>
+  <si>
     <t xml:space="preserve">212-8075-CZ</t>
   </si>
   <si>
     <t xml:space="preserve">Ceramics circle</t>
   </si>
   <si>
+    <t xml:space="preserve">e-mail SONAVOX HS KODY: „CERAMICS CIRCLE / magnetický obvod – 8518900000“</t>
+  </si>
+  <si>
     <t xml:space="preserve">IM-50196-AUDICZ</t>
   </si>
   <si>
     <t xml:space="preserve">Car Speaker</t>
   </si>
   <si>
+    <t xml:space="preserve">e-mail SONAVOX HS KODY + předchozí celní prohlášení: „SPEAKER / reproduktor – 8518210000“, CN 8518 21 00 DK 00</t>
+  </si>
+  <si>
     <t xml:space="preserve">140-80I27-42X-CZ</t>
   </si>
   <si>
@@ -457,121 +521,115 @@
     <t xml:space="preserve">KRITICKÉ</t>
   </si>
   <si>
+    <t xml:space="preserve">Dvě položky bez HS kódu – nelze proclít</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterproof membrane J2-10X002-0001-CZ (210 000 ks, 8 820,00 EUR) a Spring nut 029A-000004-CZ (30 000 ks, 540,00 EUR), obě z faktury CZ20260725. Ani jedna není v e-mailu „SONAVOX HS KODY“ ani v předchozích celních prohlášeních. Kódy NEBYLY doplněny vlastním odvozením – musí je poskytnout klient. Detail na listu „Chybějící HS kódy“.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Preferenční věta / preferenční původ (COO)</t>
   </si>
   <si>
-    <t xml:space="preserve">V žádném z dodaných dokladů (3× faktura, 3× packing list, FCR TECGO26080029, nákladní list SMGS 38055706) NENÍ uvedena preferenční věta o původu zboží. Původ zboží = ČÍNA. EU nemá s Čínou dohodu o preferenčním obchodu, preferenční sazební zacházení tedy NELZE uplatnit a při proclení se použije plná celní sazba třetí země (erga omnes). Doporučení: nevyžadovat od dodavatele preferenční prohlášení, ale potvrdit hodnotu a sazby v TARIC před podáním celního prohlášení.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incoterm – chybí místo/přístav a termín neodpovídá druhu přepravy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Všechny tři faktury i packing listy uvádějí pouze „Terms of Payment: FOB“ – BEZ uvedení přístavu / jmenovaného místa. Dvojí problém: (1) dle standardu musí být vždy uveden termín i město (např. FCA Suzhou); (2) FOB je dle Incoterms 2020 určen výhradně pro námořní a vnitrozemskou vodní přepravu, ale tato zásilka jde ŽELEZNICÍ (Zhengzhou/Putian → Malaszewicze → CZ). Pro železniční přepravu je správný termín FCA s uvedeným místem. Nutno vyžádat od odesílatele opravu / doplnění, jinak nelze spolehlivě určit, zda je do celní hodnoty nutno připočíst dopravné do hranice EU.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antidumping – závisí na materiálu A na tom, čím díl skutečně je</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Položky 14 (Nut, 029-2513-AL-CZ) a 15 (Spring nut, 029A-000004-CZ), celkem 13 140,00 EUR, mají tři možné scénáře: (a) HLINÍK → 7616 10 00, clo cca 6 %, BEZ antidumpingu; (b) OCELOVÁ MATICE → 7318 16, clo cca 3,7 %, BEZ antidumpingu; (c) OCELOVÝ ŠROUB / ZÁVITOVÁ VLOŽKA → ex 7318 15 95, clo 3,7 % + ANTIDUMPING 22,1–86,5 %. Nař. (EU) 2022/191 se vztahuje na vruty, samořezné šrouby, ostatní šrouby a svorníky s hlavou a podložky (kódy 7318 12 90, 7318 14 91, 7318 14 99, 7318 15 58, 7318 15 68, 7318 15 82, 7318 15 88, ex 7318 15 95, ex 7318 21 00, ex 7318 22 00) – kód 7318 16 pro MATICE v seznamu NENÍ, samostatné matice tedy do působnosti nespadají. Tabulka SONAVOX přiřazuje „Insert (nut)“ kód 7318 15 95 19, tj. kód pro šrouby, což u dílu nazvaného „nut“ může být chybné. V souhrnu je konzervativně ponecháno 7318 15 95 19. NUTNO ZJISTIT MATERIÁL I SKUTEČNÝ DRUH DÍLU; při variantě (c) je nutný doplňkový kód TARIC dle výrobce – bez jména výrobce se uplatní zbytková sazba 86,5 %.</t>
+    <t xml:space="preserve">V žádném z dodaných dokladů (3× faktura, 3× packing list, FCR TECGO26080029, nákladní list SMGS 38055706) NENÍ uvedena preferenční věta o původu zboží. Původ zboží = ČÍNA. EU nemá s Čínou dohodu o preferenčním obchodu, preferenční sazební zacházení tedy NELZE uplatnit a použije se plná celní sazba třetí země.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incoterm – chybí místo a termín neodpovídá druhu přepravy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Všechny tři faktury i packing listy uvádějí pouze „Terms of Payment: FOB“ – BEZ přístavu / jmenovaného místa. Navíc FOB je dle Incoterms 2020 určen jen pro námořní a vnitrozemskou vodní přepravu, ale zásilka jde ŽELEZNICÍ (Zhengzhou/Putian → Malaszewicze → CZ); správný termín je FCA s uvedeným místem. FCR je „freight collect“, takže bez určení dodacího místa nelze spolehlivě určit, zda se do celní hodnoty připočítává dopravné do hranice EU.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antidumping u matic – závisí na materiálu i na druhu dílu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Položka 14 (Nut, 029-2513-AL-CZ, 180 000 ks, 12 600,00 EUR) má dle e-mailu SONAVOX kód 7318 15 95 19. Tři možné scénáře: (a) HLINÍK → 7616 10 00, clo cca 6 %, BEZ antidumpingu; (b) OCELOVÁ MATICE → 7318 16, clo cca 3,7 %, BEZ antidumpingu; (c) OCELOVÝ ŠROUB / VLOŽKA → ex 7318 15 95, clo 3,7 % + ANTIDUMPING 22,1–86,5 %. Nař. (EU) 2022/191 se vztahuje na vruty, samořezné šrouby, ostatní šrouby a svorníky s hlavou a podložky (7318 12 90, 7318 14 91, 7318 14 99, 7318 15 58, 7318 15 68, 7318 15 82, 7318 15 88, ex 7318 15 95, ex 7318 21 00, ex 7318 22 00) – kód 7318 16 pro MATICE v seznamu NENÍ. Bez jména čínského výrobce se uplatní zbytková sazba 86,5 %. NUTNO ZJISTIT MATERIÁL, DRUH DÍLU A VÝROBCE.</t>
   </si>
   <si>
     <t xml:space="preserve">CBAM – platí u matic v každé variantě</t>
   </si>
   <si>
-    <t xml:space="preserve">Položky 14 a 15 (210 000 ks, čistá hmotnost 312,30 kg) spadají do přílohy I nařízení CBAM bez ohledu na to, jak dopadne otázka materiálu: kapitola 73 (železo a ocel) i kapitola 76 (hliník) jsou v příloze I. Nutno zahrnout do čtvrtletního CBAM hlášení (vykazuje se čistá hmotnost a zabudované emise). Ostatní položky zásilky (kap. 35, 39, 85) do CBAM nespadají.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nesoulad: „Nut 029-2513-AL-CZ“ – ocel nebo hliník?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Označení dílu obsahuje „-AL-“, což naznačuje HLINÍK, avšak podklad SONAVOX (e-mail „SONAVOX HS KODY“) přiřazuje „Insert (nut)“ kód 7318 15 95 19 (železo/ocel). Hliníková matice by patřila pod 7616 10 00. Zařazení má přímý dopad: 7318 = antidumping ANO + CBAM ANO; 7616 = antidumping NE + CBAM ANO. V souhrnu je konzervativně použito 7318 15 95 19. NUTNO POTVRDIT MATERIÁL I DRUH DÍLU U DODAVATELE (matice vs. závitová vložka/šroub) – viz poznámka k antidumpingu.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VYŘEŠENO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Přípona u 8518 90 00 = DK 00 (opraveno dle předchozích celních prohlášení)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Referenční tabulka SONAVOX uvádí u částí reproduktorů souběžně přípony 00, 40, 90 i 99. Ve dvou předchozích celních prohlášeních Sonavox je však pro VŠECHNY části reproduktorů použito jednotně 8518 90 00 s doplňkovým kódem DK 00 – včetně Front plate („Front plate – deska“), T-yoke, Cone, Spider, Dust cap a Bracket. Front plate byl proto v tomto souhrnu OPRAVEN z 8518 9000 90 na 8518 9000 00. Přípony 40 / 90 / 99 z tabulky SONAVOX se v praxi nepoužívají.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterproof membrane – kód přiřazen odvozením</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Položka 9 (J2-10X002-0001-CZ, Waterproof membrane, 210 000 ks, 8 820,00 EUR) není v referenční tabulce SONAVOX uvedena pod tímto názvem. Byl použit kód 3921 90 90 90 podle nejbližší položky „Protective membrane plast / Plastová membrána“. Doporučeno potvrdit u dodavatele.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terminal – OPRAVENO z 7409 39 00 na 8518 90 00 00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Položky 10–13 (Terminal, celkem 600 000 ks, 9 380,00 EUR) byly původně zařazeny pod 7409 39 00 podle položky „Pin, lug / kontakt“ z tabulky SONAVOX. Předchozí celní prohlášení Sonavox však deklaruje „terminal – části reproduktorů“ pod 8518 90 00 DK 00. Zařazení bylo opraveno na 8518 90 00 00, což je i věcně správnější (hotový díl určený výhradně pro reproduktor = část zboží čísla 8518 dle pozn. 2 ke třídě XVI; 7409 je naopak polotovar – desky a pásy z mědi).</t>
+    <t xml:space="preserve">Položka 14 (180 000 ks, čistá hmotnost 299,70 kg) spadá do přílohy I nařízení CBAM bez ohledu na výsledek otázky materiálu – kapitola 73 (železo a ocel) i kapitola 76 (hliník) jsou v příloze I. Nutno zahrnout do čtvrtletního CBAM hlášení. Pokud bude Spring nut zařazen do stejné kapitoly, platí totéž i pro něj. Ostatní položky zásilky (kap. 39, 85) do CBAM nespadají.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROZPOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Front plate – e-mail a celní prohlášení se liší</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-mail SONAVOX uvádí u „FRONT PLATE / ocelová deska“ kód 8518900090. Předchozí celní prohlášení Sonavox však deklaruje „Front plate – deska“ pod CN 8518 90 00 s DK 00. V souhrnu je použita varianta z celního prohlášení (8518 9000 00), protože jde o skutečně přijaté prohlášení. Přípony 40 / 90 / 99, které e-mail u 8518 90 00 používá, se v žádném z prohlášení nevyskytují – vždy je tam DK 00. POKUD MÁ PLATIT VARIANTA Z E-MAILU, JE NUTNO ŘÁDEK OPRAVIT.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminal – e-mail a celní prohlášení se liší</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-mail SONAVOX nemá řádek „Terminal“; nejbližší je „Pin, lug / kontakt – 74093900“. Předchozí celní prohlášení však deklaruje přímo „terminal – části reproduktorů“ pod CN 8518 90 00 DK 00. V souhrnu je použit kód z celního prohlášení, protože odpovídá názvu položky doslova.</t>
   </si>
   <si>
     <t xml:space="preserve">NESROVNALOST</t>
   </si>
   <si>
-    <t xml:space="preserve">FCR uvádí jen jednoho odesílatele, zásilka je však od tří prodávajících</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FCR TECGO26080029 uvádí jako shipper pouze SUZHOU SONAVOX ELECTRONICS CO., LTD. Zboží v kontejneru však pochází od TŘÍ různých prodávajících (Suzhou Sonavox International Trading, Suzhou Sonavox Electronics, Suzhou Yanlong Electronic Product) dle tří samostatných faktur. Celní prohlášení musí být členěno dle jednotlivých odesílatelů – proto je souhrn zpracován primárně dle odesílatele.</t>
+    <t xml:space="preserve">FCR uvádí jen jednoho odesílatele, zásilka je od tří prodávajících</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FCR TECGO26080029 uvádí jako shipper pouze SUZHOU SONAVOX ELECTRONICS CO., LTD, zboží však pochází od tří různých prodávajících dle tří samostatných faktur. Souhrn je proto členěn dle odesílatele.</t>
   </si>
   <si>
     <t xml:space="preserve">Popis zboží ve FCR neuvádí všechny položky</t>
   </si>
   <si>
-    <t xml:space="preserve">FCR vyjmenovává: Speaker component, Speaker, Voice coil, Front plate, Gasket, Waterproof membrane, Terminal, Nut, Spring nut, Harness, Gauge, Cone. CHYBÍ zde SPIDER (středící membrána, 77 600 ks) a CERAMICS CIRCLE (magnetický obvod, 19 152 ks) – zřejmě jsou zahrnuty pod obecné „Speaker component“, ale doporučeno upozornit dopravce.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nákladní list SMGS deklaruje celý kontejner pod jedním kódem 8518 90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMGS 38055706 uvádí HS 851890 / 85189000 „Speaker component“ (+ HS 99020000 sběrné zboží) pro celý kontejner. Skutečné zboží však spadá do kapitol 35, 39, 73, 74 a 85. Jde o zjednodušení přepravního dokladu, které nemá vliv na celní zařazení, ale může vyvolat dotaz celního úřadu – vhodné mít připravené rozúčtování dle faktur.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rozdílná čísla bankovních účtů mezi packing listem a fakturou (CZ20260725)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U dokladu CZ20260725 (Suzhou Sonavox International Trading) uvádí packing list účet EUR 500158216108, zatímco faktura uvádí EUR 468960663282. Nemá vliv na celní řízení, ale před úhradou doporučeno ověřit správné číslo účtu přímo u dodavatele (riziko podvodné změny platebních údajů).</t>
+    <t xml:space="preserve">FCR vyjmenovává: Speaker component, Speaker, Voice coil, Front plate, Gasket, Waterproof membrane, Terminal, Nut, Spring nut, Harness, Gauge, Cone. CHYBÍ SPIDER (77 600 ks) a CERAMICS CIRCLE (19 152 ks) – zřejmě zahrnuty pod obecné „Speaker component“.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nákladní list SMGS deklaruje celý kontejner pod jedním kódem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMGS 38055706 uvádí HS 851890 / 85189000 „Speaker component“ (+ HS 99020000) pro celý kontejner, ačkoli zboží spadá do kapitol 39, 73 a 85. Přepravní zjednodušení bez vlivu na celní zařazení, může však vyvolat dotaz celního úřadu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rozdílná čísla bankovních účtů (CZ20260725)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Packing list uvádí účet EUR 500158216108, faktura EUR 468960663282. Bez vlivu na celní řízení, ale před úhradou ověřit u dodavatele.</t>
   </si>
   <si>
     <t xml:space="preserve">ETD/ETA neodpovídá datu vypravení</t>
   </si>
   <si>
-    <t xml:space="preserve">Packing list CZ20260725-2 (Yanlong) uvádí ETD 29.07.2026 / ETA 29.08.2026; FCR byl však vystaven 04.08.2026 a vlak má č. V.WB2026/08/05 (05.08.2026). U zbylých dvou sad dokladů jsou ETD/ETA prázdné. Doporučeno sjednotit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Potvrzeno předchozími celními prohlášeními Sonavox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z dvou předchozích celních prohlášení na obdobné zásilky Sonavox byly potvrzeny tyto kódy: Cone, Spider, Dust cap, T-yoke, Front plate, Bracket, Speaker component i Terminal = 8518 90 00 DK 00; Car speaker = 8518 21 00 DK 00; Harness / kabelový svazek = 7413 00 00 DK 90; Gasket (plastové těsnění) + Gauge (plastový kalibr) společně na jednom řádku = 3926 90 97 DK 90. Potvrzen je rovněž postup slučování více komponent pod jeden kód na jeden řádek.</t>
+    <t xml:space="preserve">Packing list CZ20260725-2 uvádí ETD 29.07.2026 / ETA 29.08.2026; FCR byl vystaven 04.08.2026 a vlak má č. V.WB2026/08/05. U zbylých dvou sad dokladů jsou ETD/ETA prázdné.</t>
   </si>
   <si>
     <t xml:space="preserve">OK</t>
   </si>
   <si>
+    <t xml:space="preserve">Faktury a packing listy spolu souhlasí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porovnáno po položkách: 19 / 2 / 3 řádků v obou dokladech každé sady, shodná čísla dílů, množství i popisy. Žádná položka není jen na faktuře nebo jen na packing listu.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kontrolní součty souhlasí</t>
   </si>
   <si>
-    <t xml:space="preserve">Hrubá hmotnost 9 950,74 + 12 907,84 + 1 274,42 = 24 133,00 kg = FCR (24 133 KGS) i SMGS (24 133 kg). Kolí 12 + 23 + 16 = 51 palet = FCR (51 PLTS) i SMGS (51). Objem 15,24 + 16,64 + 19,52 = 51,40 CBM = FCR (51,4 CBM). Množství i celní hodnota souhlasí s fakturami.</t>
+    <t xml:space="preserve">Hrubá hmotnost 9 950,74 + 12 907,84 + 1 274,42 = 24 133,00 kg = FCR i SMGS. Kolí 12 + 23 + 16 = 51 palet. Objem 15,24 + 16,64 + 19,52 = 51,40 CBM = FCR. Množství i celní hodnota souhlasí s fakturami.</t>
   </si>
   <si>
     <t xml:space="preserve">Sleva / rabat</t>
   </si>
   <si>
-    <t xml:space="preserve">V žádné z faktur není uvedena obchodní sleva ani rabat; součet položek = Sub Total. Poměrné rozpuštění slevy do celní hodnoty se tedy neuplatňuje.</t>
+    <t xml:space="preserve">V žádné faktuře není uvedena obchodní sleva ani rabat; součet položek = Sub Total. Poměrné rozpuštění slevy do celní hodnoty se neuplatňuje.</t>
   </si>
   <si>
     <t xml:space="preserve">INFO</t>
   </si>
   <si>
-    <t xml:space="preserve">Dopravné / celní hodnota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FCR uvádí FREIGHT COLLECT (dopravné hradí příjemce) a fakturační podmínka je FOB. Do celní hodnoty je proto nutno připočíst náklady dopravy a pojištění do místa vstupu do EU (hranice EU – Malaszewicze/PL). Podklady k dopravnému nebyly součástí dodaných dokladů.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZDROJOVÉ DOKLADY A PŘIŘAZENÍ HS KÓDŮ</t>
+    <t xml:space="preserve">Kódy nebyly nikdy doplňovány vlastním odvozením</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Každý HS kód v tomto souhrnu je doslovně převzat z e-mailu „SONAVOX HS KODY“ nebo z předchozího celního prohlášení Sonavox; zdroj je uveden u každého řádku ve sloupci „Zdroj HS kódu“ a na listu Line items. Kde podklad chybí, zůstává kód prázdný. Platnost kódů nebyla ověřena přímo v databázi TARIC – doporučeno před podáním prohlášení zkontrolovat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZDROJOVÉ DOKLADY</t>
   </si>
   <si>
     <t xml:space="preserve">Doklad</t>
@@ -580,52 +638,58 @@
     <t xml:space="preserve">Obsah / použití</t>
   </si>
   <si>
-    <t xml:space="preserve">TRCZ20260725.xlsx (listy PL, INV)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Faktura + packing list CZ20260725 – Suzhou Sonavox International Trading Co., Ltd (19 položek)</t>
+    <t xml:space="preserve">TRCZ20260725.xlsx (PL, INV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faktura + packing list CZ20260725 – Suzhou Sonavox International Trading (19 položek)</t>
   </si>
   <si>
     <t xml:space="preserve">ELCZ202607251_...GCS.xlsx (2 soubory)</t>
   </si>
   <si>
-    <t xml:space="preserve">Faktura + packing list CZ20260725-1 – Suzhou Sonavox Electronics Co., Ltd (2 položky)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YLCZ202607252.xlsx (listy PL, INV)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Faktura + packing list CZ20260725-2 – Suzhou Yanlong Electronic Product Co., Ltd (3 položky)</t>
+    <t xml:space="preserve">Faktura + packing list CZ20260725-1 – Suzhou Sonavox Electronics (2 položky)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YLCZ202607252.xlsx (PL, INV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faktura + packing list CZ20260725-2 – Suzhou Yanlong Electronic Product (3 položky)</t>
   </si>
   <si>
     <t xml:space="preserve">HBL_TECGO26080029.pdf</t>
   </si>
   <si>
-    <t xml:space="preserve">Forwarder's Cargo Receipt T.H.I. Group Ltd. – trasa, kontejner, brutto, kolí, objem</t>
+    <t xml:space="preserve">Forwarder's Cargo Receipt T.H.I. Group – trasa, kontejner, brutto, kolí, objem</t>
   </si>
   <si>
     <t xml:space="preserve">CIMU1716969.pdf</t>
   </si>
   <si>
-    <t xml:space="preserve">Nákladní list SMGS č. 38055706 – železniční přeprava, plomba, hmotnosti, trasa</t>
+    <t xml:space="preserve">Nákladní list SMGS 38055706 – železniční přeprava, plomba, hmotnosti, trasa</t>
   </si>
   <si>
     <t xml:space="preserve">Re_SONAVOX_HS_KODY.eml</t>
   </si>
   <si>
-    <t xml:space="preserve">Referenční tabulka HS kódů s českými popisy (Ing. Michaela Ryan, Sonavox Technology CZ) – zdroj HS kódů a českých popisů</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Předchozí celní prohlášení Sonavox (2 ks)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Screenshoty položek dřívějších celních prohlášení na obdobné zásilky – zdroj potvrzení kódů 8518 90 00 DK 00, 8518 21 00 DK 00, 7413 00 00 DK 90 a 3926 90 97 DK 90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POZOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Faktury ANI packing listy neobsahují žádné HS kódy. Kódy v tomto souhrnu pocházejí z referenční tabulky „SONAVOX HS KODY“ a z předchozích celních prohlášení Sonavox. Kde se oba zdroje liší, má přednost celní prohlášení (Front plate, Terminal). Zbývající nepotvrzené položky jsou na listu Poznámky &amp; flagy označeny jako „K OVĚŘENÍ“: Nut / Spring nut (materiál) a Waterproof membrane. Voice coil je podložen závaznou informací o sazebním zařazení ZISZ 30-0292-2016.</t>
+    <t xml:space="preserve">Referenční tabulka HS kódů s českými popisy (Ing. Michaela Ryan, Sonavox Technology CZ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Předchozí celní prohlášení Sonavox (2×)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Položky dřívějších prohlášení na obdobné zásilky – zdroj kódů 8518 90 00 DK 00, 8518 21 00 DK 00, 7413 00 00 DK 90, 3926 90 97 DK 90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-mail Josef Šrejber, OR: CZ26011282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zadání k vyclení – reference, celnice A1 Ostrava, režim volný oběh, příjezd 34. týden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRAVIDLO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS kódy se v tomto souhrnu NEVYTVÁŘEJÍ vlastním odvozením. Použit je pouze kód doslovně uvedený v některém z výše uvedených podkladů; zdroj je zaznamenán u každého řádku. Položky bez podkladu zůstávají bez kódu a vyžadují se od klienta – list „Chybějící HS kódy“.</t>
   </si>
 </sst>
 </file>
@@ -698,7 +762,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -735,6 +799,12 @@
         <bgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
@@ -834,7 +904,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -886,24 +956,24 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -947,11 +1017,19 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF1F4E79"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCE4E4"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -967,6 +1045,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC00000"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1219,20 +1305,20 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1321,10 +1407,10 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1337,18 +1423,18 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1420,7 +1506,7 @@
         <v>9841</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J19" s="7" t="s">
         <v>45</v>
@@ -1462,7 +1548,7 @@
         <v>32182.14</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J20" s="7" t="s">
         <v>45</v>
@@ -1504,7 +1590,7 @@
         <v>1378.1</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J21" s="7" t="s">
         <v>45</v>
@@ -1517,232 +1603,232 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="13" t="n">
         <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A22,'Line items'!$F$2:$F$25,$C22)</f>
+        <v>180000</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A22,'Line items'!$F$2:$F$25,$C22)</f>
+        <v>299.7</v>
+      </c>
+      <c r="G22" s="14" t="n">
+        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A22,'Line items'!$F$2:$F$25,$C22)</f>
+        <v>310.5</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A22,'Line items'!$F$2:$F$25,$C22)</f>
+        <v>12600</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="K22" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A23,'Line items'!$F$2:$F$25,$C23)</f>
+        <v>51200</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A23,'Line items'!$F$2:$F$25,$C23)</f>
+        <v>235.52</v>
+      </c>
+      <c r="G23" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A23,'Line items'!$F$2:$F$25,$C23)</f>
+        <v>250</v>
+      </c>
+      <c r="H23" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A23,'Line items'!$F$2:$F$25,$C23)</f>
+        <v>8120.32</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" s="13" t="n">
+        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A24,'Line items'!$D$2:$D$25,"J2-10X002-0001-CZ")</f>
         <v>210000</v>
       </c>
-      <c r="F22" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A22,'Line items'!$F$2:$F$25,$C22)</f>
+      <c r="F24" s="14" t="n">
+        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A24,'Line items'!$D$2:$D$25,"J2-10X002-0001-CZ")</f>
         <v>30.24</v>
       </c>
-      <c r="G22" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A22,'Line items'!$F$2:$F$25,$C22)</f>
+      <c r="G24" s="14" t="n">
+        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A24,'Line items'!$D$2:$D$25,"J2-10X002-0001-CZ")</f>
         <v>40</v>
       </c>
-      <c r="H22" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A22,'Line items'!$F$2:$F$25,$C22)</f>
+      <c r="H24" s="14" t="n">
+        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A24,'Line items'!$D$2:$D$25,"J2-10X002-0001-CZ")</f>
         <v>8820</v>
       </c>
-      <c r="I22" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="L22" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11" t="s">
+      <c r="I24" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B25" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C25" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A25,'Line items'!$D$2:$D$25,"029A-000004-CZ")</f>
+        <v>30000</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A25,'Line items'!$D$2:$D$25,"029A-000004-CZ")</f>
+        <v>12.6</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A25,'Line items'!$D$2:$D$25,"029A-000004-CZ")</f>
+        <v>15</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A25,'Line items'!$D$2:$D$25,"029A-000004-CZ")</f>
+        <v>540</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D23" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="E23" s="13" t="n">
-        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A23,'Line items'!$F$2:$F$25,$C23)</f>
-        <v>210000</v>
-      </c>
-      <c r="F23" s="14" t="n">
-        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A23,'Line items'!$F$2:$F$25,$C23)</f>
-        <v>312.3</v>
-      </c>
-      <c r="G23" s="14" t="n">
-        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A23,'Line items'!$F$2:$F$25,$C23)</f>
-        <v>325.5</v>
-      </c>
-      <c r="H23" s="14" t="n">
-        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A23,'Line items'!$F$2:$F$25,$C23)</f>
-        <v>13140</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="J23" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="K23" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="L23" s="11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A24,'Line items'!$F$2:$F$25,$C24)</f>
-        <v>51200</v>
-      </c>
-      <c r="F24" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A24,'Line items'!$F$2:$F$25,$C24)</f>
-        <v>235.52</v>
-      </c>
-      <c r="G24" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A24,'Line items'!$F$2:$F$25,$C24)</f>
-        <v>250</v>
-      </c>
-      <c r="H24" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A24,'Line items'!$F$2:$F$25,$C24)</f>
-        <v>8120.32</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="K24" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="L24" s="7" t="s">
+      <c r="K25" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="L25" s="11" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="E25" s="18" t="n">
-        <f aca="false">SUM(E19:E24)</f>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <f aca="false">SUM(E19:E25)</f>
         <v>1324160</v>
       </c>
-      <c r="F25" s="19" t="n">
-        <f aca="false">SUM(F19:F24)</f>
+      <c r="F26" s="19" t="n">
+        <f aca="false">SUM(F19:F25)</f>
         <v>9574.05</v>
       </c>
-      <c r="G25" s="19" t="n">
-        <f aca="false">SUM(G19:G24)</f>
+      <c r="G26" s="19" t="n">
+        <f aca="false">SUM(G19:G25)</f>
         <v>9950.74</v>
       </c>
-      <c r="H25" s="19" t="n">
-        <f aca="false">SUM(H19:H24)</f>
+      <c r="H26" s="19" t="n">
+        <f aca="false">SUM(H19:H25)</f>
         <v>73481.56</v>
       </c>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-    </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A26,'Line items'!$F$2:$F$25,$C26)</f>
-        <v>19152</v>
-      </c>
-      <c r="F26" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A26,'Line items'!$F$2:$F$25,$C26)</f>
-        <v>11299.68</v>
-      </c>
-      <c r="G26" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A26,'Line items'!$F$2:$F$25,$C26)</f>
-        <v>11688.8</v>
-      </c>
-      <c r="H26" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A26,'Line items'!$F$2:$F$25,$C26)</f>
-        <v>19918.08</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="L26" s="7" t="s">
-        <v>49</v>
-      </c>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C27" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>68</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>69</v>
       </c>
       <c r="E27" s="9" t="n">
         <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A27,'Line items'!$F$2:$F$25,$C27)</f>
-        <v>2016</v>
+        <v>19152</v>
       </c>
       <c r="F27" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A27,'Line items'!$F$2:$F$25,$C27)</f>
-        <v>1149.12</v>
+        <v>11299.68</v>
       </c>
       <c r="G27" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A27,'Line items'!$F$2:$F$25,$C27)</f>
-        <v>1219.04</v>
+        <v>11688.8</v>
       </c>
       <c r="H27" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A27,'Line items'!$F$2:$F$25,$C27)</f>
-        <v>5140.8</v>
+        <v>19918.08</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J27" s="7" t="s">
         <v>45</v>
@@ -1751,163 +1837,189 @@
         <v>45</v>
       </c>
       <c r="L27" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="17" t="s">
+      <c r="E28" s="9" t="n">
+        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A28,'Line items'!$F$2:$F$25,$C28)</f>
+        <v>2016</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A28,'Line items'!$F$2:$F$25,$C28)</f>
+        <v>1149.12</v>
+      </c>
+      <c r="G28" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A28,'Line items'!$F$2:$F$25,$C28)</f>
+        <v>1219.04</v>
+      </c>
+      <c r="H28" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A28,'Line items'!$F$2:$F$25,$C28)</f>
+        <v>5140.8</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="L28" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E28" s="18" t="n">
-        <f aca="false">SUM(E26:E27)</f>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="16"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="E29" s="18" t="n">
+        <f aca="false">SUM(E27:E28)</f>
         <v>21168</v>
       </c>
-      <c r="F28" s="19" t="n">
-        <f aca="false">SUM(F26:F27)</f>
+      <c r="F29" s="19" t="n">
+        <f aca="false">SUM(F27:F28)</f>
         <v>12448.8</v>
       </c>
-      <c r="G28" s="19" t="n">
-        <f aca="false">SUM(G26:G27)</f>
+      <c r="G29" s="19" t="n">
+        <f aca="false">SUM(G27:G28)</f>
         <v>12907.84</v>
       </c>
-      <c r="H28" s="19" t="n">
-        <f aca="false">SUM(H26:H27)</f>
+      <c r="H29" s="19" t="n">
+        <f aca="false">SUM(H27:H28)</f>
         <v>25058.88</v>
       </c>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-    </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B29" s="7" t="s">
+      <c r="I29" s="16"/>
+      <c r="J29" s="16"/>
+      <c r="K29" s="16"/>
+      <c r="L29" s="16"/>
+    </row>
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="B30" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D29" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E29" s="9" t="n">
-        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A29,'Line items'!$F$2:$F$25,$C29)</f>
+      <c r="D30" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A30,'Line items'!$F$2:$F$25,$C30)</f>
         <v>43760</v>
       </c>
-      <c r="F29" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A29,'Line items'!$F$2:$F$25,$C29)</f>
+      <c r="F30" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A30,'Line items'!$F$2:$F$25,$C30)</f>
         <v>957</v>
       </c>
-      <c r="G29" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A29,'Line items'!$F$2:$F$25,$C29)</f>
+      <c r="G30" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A30,'Line items'!$F$2:$F$25,$C30)</f>
         <v>1274.42</v>
       </c>
-      <c r="H29" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A29,'Line items'!$F$2:$F$25,$C29)</f>
+      <c r="H30" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A30,'Line items'!$F$2:$F$25,$C30)</f>
         <v>20830.64</v>
       </c>
-      <c r="I29" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J29" s="7" t="s">
+      <c r="I30" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J30" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="K29" s="7" t="s">
+      <c r="K30" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L29" s="7" t="s">
+      <c r="L30" s="7" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="16"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="E30" s="18" t="n">
-        <f aca="false">SUM(E29:E29)</f>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="16"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <f aca="false">SUM(E30:E30)</f>
         <v>43760</v>
       </c>
-      <c r="F30" s="19" t="n">
-        <f aca="false">SUM(F29:F29)</f>
+      <c r="F31" s="19" t="n">
+        <f aca="false">SUM(F30:F30)</f>
         <v>957</v>
       </c>
-      <c r="G30" s="19" t="n">
-        <f aca="false">SUM(G29:G29)</f>
+      <c r="G31" s="19" t="n">
+        <f aca="false">SUM(G30:G30)</f>
         <v>1274.42</v>
       </c>
-      <c r="H30" s="19" t="n">
-        <f aca="false">SUM(H29:H29)</f>
+      <c r="H31" s="19" t="n">
+        <f aca="false">SUM(H30:H30)</f>
         <v>20830.64</v>
       </c>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="20"/>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="E31" s="22" t="n">
-        <f aca="false">E25+E28+E30</f>
+      <c r="I31" s="16"/>
+      <c r="J31" s="16"/>
+      <c r="K31" s="16"/>
+      <c r="L31" s="16"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="E32" s="22" t="n">
+        <f aca="false">E26+E29+E31</f>
         <v>1389088</v>
       </c>
-      <c r="F31" s="23" t="n">
-        <f aca="false">F25+F28+F30</f>
+      <c r="F32" s="23" t="n">
+        <f aca="false">F26+F29+F31</f>
         <v>22979.85</v>
       </c>
-      <c r="G31" s="23" t="n">
-        <f aca="false">G25+G28+G30</f>
+      <c r="G32" s="23" t="n">
+        <f aca="false">G26+G29+G31</f>
         <v>24133</v>
       </c>
-      <c r="H31" s="23" t="n">
-        <f aca="false">H25+H28+H30</f>
+      <c r="H32" s="23" t="n">
+        <f aca="false">H26+H29+H31</f>
         <v>119371.08</v>
       </c>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B33" s="2" t="s">
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="20"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="B34" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="C34" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
+      <c r="D34" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="B34" s="24" t="n">
-        <f aca="false">E31</f>
-        <v>1389088</v>
-      </c>
-      <c r="C34" s="24" t="n">
-        <v>1389088</v>
-      </c>
-      <c r="D34" s="24" t="n">
-        <f aca="false">B34-C34</f>
-        <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1915,11 +2027,11 @@
         <v>82</v>
       </c>
       <c r="B35" s="24" t="n">
-        <f aca="false">F31</f>
-        <v>22979.85</v>
+        <f aca="false">E32</f>
+        <v>1389088</v>
       </c>
       <c r="C35" s="24" t="n">
-        <v>22979.85</v>
+        <v>1389088</v>
       </c>
       <c r="D35" s="24" t="n">
         <f aca="false">B35-C35</f>
@@ -1931,11 +2043,11 @@
         <v>83</v>
       </c>
       <c r="B36" s="24" t="n">
-        <f aca="false">G31</f>
-        <v>24133</v>
+        <f aca="false">F32</f>
+        <v>22979.85</v>
       </c>
       <c r="C36" s="24" t="n">
-        <v>24133</v>
+        <v>22979.85</v>
       </c>
       <c r="D36" s="24" t="n">
         <f aca="false">B36-C36</f>
@@ -1947,14 +2059,30 @@
         <v>84</v>
       </c>
       <c r="B37" s="24" t="n">
-        <f aca="false">H31</f>
-        <v>119371.08</v>
+        <f aca="false">G32</f>
+        <v>24133</v>
       </c>
       <c r="C37" s="24" t="n">
-        <v>119371.08</v>
+        <v>24133</v>
       </c>
       <c r="D37" s="24" t="n">
         <f aca="false">B37-C37</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" s="24" t="n">
+        <f aca="false">H32</f>
+        <v>119371.08</v>
+      </c>
+      <c r="C38" s="24" t="n">
+        <v>119371.08</v>
+      </c>
+      <c r="D38" s="24" t="n">
+        <f aca="false">B38-C38</f>
         <v>0</v>
       </c>
     </row>
@@ -1974,893 +2102,1133 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>210000</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>8820</v>
+      </c>
+      <c r="J5" s="26"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>540</v>
+      </c>
+      <c r="J6" s="26"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E7" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F7" s="27" t="n">
+        <f aca="false">SUM(F5:F6)</f>
+        <v>240000</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <f aca="false">SUM(G5:G6)</f>
+        <v>42.84</v>
+      </c>
+      <c r="H7" s="28" t="n">
+        <f aca="false">SUM(H5:H6)</f>
+        <v>55</v>
+      </c>
+      <c r="I7" s="28" t="n">
+        <f aca="false">SUM(I5:I6)</f>
+        <v>9360</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:L26"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="C1" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="D1" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="E1" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="F1" s="25" t="s">
+      <c r="A1" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="E1" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="I1" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="J1" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="K1" s="25" t="s">
-        <v>94</v>
+      <c r="H1" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="I1" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="J1" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="K1" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="L1" s="29" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="26" t="n">
+      <c r="C2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="F2" s="27" t="s">
+      <c r="D2" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>43</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="H2" s="28" t="n">
+      <c r="H2" s="9" t="n">
         <v>65000</v>
       </c>
-      <c r="I2" s="29" t="n">
+      <c r="I2" s="10" t="n">
         <v>86.5</v>
       </c>
-      <c r="J2" s="29" t="n">
+      <c r="J2" s="10" t="n">
         <v>216.33</v>
       </c>
-      <c r="K2" s="29" t="n">
+      <c r="K2" s="10" t="n">
         <v>9841</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
+      <c r="L2" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="26" t="n">
+      <c r="C3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>35000</v>
+      </c>
+      <c r="I3" s="10" t="n">
+        <v>2345</v>
+      </c>
+      <c r="J3" s="10" t="n">
+        <v>2385</v>
+      </c>
+      <c r="K3" s="10" t="n">
+        <v>3542</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>32400</v>
+      </c>
+      <c r="I4" s="10" t="n">
+        <v>5103</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>5183</v>
+      </c>
+      <c r="K4" s="10" t="n">
+        <v>7464.96</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>1012.5</v>
+      </c>
+      <c r="J5" s="10" t="n">
+        <v>1032.91</v>
+      </c>
+      <c r="K5" s="10" t="n">
+        <v>1377.5</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>5600</v>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J6" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="K6" s="10" t="n">
+        <v>449.68</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>72000</v>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>7041.6</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="J8" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="K8" s="10" t="n">
+        <v>2926.4</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>75000</v>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="J9" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="K9" s="10" t="n">
+        <v>1612.5</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>125000</v>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>2687.5</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>110</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>2540</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>110</v>
+      </c>
+      <c r="K12" s="10" t="n">
+        <v>2540</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>960</v>
+      </c>
+      <c r="I13" s="10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J13" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="K14" s="10" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>57.78</v>
+      </c>
+      <c r="J15" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>899.5</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>23.11</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="K16" s="10" t="n">
+        <v>302</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>180000</v>
+      </c>
+      <c r="I17" s="10" t="n">
+        <v>299.7</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>310.5</v>
+      </c>
+      <c r="K17" s="10" t="n">
+        <v>12600</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>51200</v>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>235.52</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>250</v>
+      </c>
+      <c r="K18" s="10" t="n">
+        <v>8120.32</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>210000</v>
+      </c>
+      <c r="I19" s="14" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="K19" s="14" t="n">
+        <v>8820</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E20" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="F20" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="K20" s="14" t="n">
+        <v>540</v>
+      </c>
+      <c r="L20" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="F21" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="H3" s="28" t="n">
-        <v>35000</v>
-      </c>
-      <c r="I3" s="29" t="n">
-        <v>2345</v>
-      </c>
-      <c r="J3" s="29" t="n">
-        <v>2385</v>
-      </c>
-      <c r="K3" s="29" t="n">
-        <v>3542</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="26" t="n">
+      <c r="G21" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>19152</v>
+      </c>
+      <c r="I21" s="10" t="n">
+        <v>11299.68</v>
+      </c>
+      <c r="J21" s="10" t="n">
+        <v>11688.8</v>
+      </c>
+      <c r="K21" s="10" t="n">
+        <v>19918.08</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>2016</v>
+      </c>
+      <c r="I22" s="10" t="n">
+        <v>1149.12</v>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v>1219.04</v>
+      </c>
+      <c r="K22" s="10" t="n">
+        <v>5140.8</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>33600</v>
+      </c>
+      <c r="I23" s="10" t="n">
+        <v>856.8</v>
+      </c>
+      <c r="J23" s="10" t="n">
+        <v>1134</v>
+      </c>
+      <c r="K23" s="10" t="n">
+        <v>16836.96</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>2160</v>
+      </c>
+      <c r="I24" s="10" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="J24" s="10" t="n">
+        <v>84.12</v>
+      </c>
+      <c r="K24" s="10" t="n">
+        <v>1280.88</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="E4" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="F4" s="27" t="s">
+      <c r="D25" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="F25" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="H4" s="28" t="n">
-        <v>32400</v>
-      </c>
-      <c r="I4" s="29" t="n">
-        <v>5103</v>
-      </c>
-      <c r="J4" s="29" t="n">
-        <v>5183</v>
-      </c>
-      <c r="K4" s="29" t="n">
-        <v>7464.96</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="F5" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="H5" s="28" t="n">
-        <v>25000</v>
-      </c>
-      <c r="I5" s="29" t="n">
-        <v>1012.5</v>
-      </c>
-      <c r="J5" s="29" t="n">
-        <v>1032.91</v>
-      </c>
-      <c r="K5" s="29" t="n">
-        <v>1377.5</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="26" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="F6" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="H6" s="28" t="n">
-        <v>5600</v>
-      </c>
-      <c r="I6" s="29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J6" s="29" t="n">
-        <v>15</v>
-      </c>
-      <c r="K6" s="29" t="n">
-        <v>449.68</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="26" t="n">
-        <v>6</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="F7" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="H7" s="28" t="n">
-        <v>72000</v>
-      </c>
-      <c r="I7" s="29" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="J7" s="29" t="n">
-        <v>25</v>
-      </c>
-      <c r="K7" s="29" t="n">
-        <v>7041.6</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="26" t="n">
-        <v>19</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="F8" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="H8" s="28" t="n">
+      <c r="G25" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="H25" s="9" t="n">
         <v>8000</v>
       </c>
-      <c r="I8" s="29" t="n">
-        <v>16</v>
-      </c>
-      <c r="J8" s="29" t="n">
-        <v>20</v>
-      </c>
-      <c r="K8" s="29" t="n">
-        <v>2926.4</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="26" t="n">
-        <v>7</v>
-      </c>
-      <c r="D9" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="F9" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="H9" s="28" t="n">
-        <v>960</v>
-      </c>
-      <c r="I9" s="29" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J9" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="K9" s="29" t="n">
-        <v>100.8</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="26" t="n">
-        <v>8</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="F10" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="H10" s="28" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I10" s="29" t="n">
-        <v>15</v>
-      </c>
-      <c r="J10" s="29" t="n">
-        <v>20</v>
-      </c>
-      <c r="K10" s="29" t="n">
-        <v>75.8</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="26" t="n">
-        <v>17</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="F11" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="H11" s="28" t="n">
-        <v>5000</v>
-      </c>
-      <c r="I11" s="29" t="n">
-        <v>57.78</v>
-      </c>
-      <c r="J11" s="29" t="n">
-        <v>70</v>
-      </c>
-      <c r="K11" s="29" t="n">
-        <v>899.5</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="26" t="n">
-        <v>18</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="F12" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="H12" s="28" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I12" s="29" t="n">
-        <v>23.11</v>
-      </c>
-      <c r="J12" s="29" t="n">
-        <v>28</v>
-      </c>
-      <c r="K12" s="29" t="n">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="26" t="n">
-        <v>9</v>
-      </c>
-      <c r="D13" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="E13" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="F13" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="H13" s="28" t="n">
-        <v>210000</v>
-      </c>
-      <c r="I13" s="29" t="n">
-        <v>30.24</v>
-      </c>
-      <c r="J13" s="29" t="n">
-        <v>40</v>
-      </c>
-      <c r="K13" s="29" t="n">
-        <v>8820</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="26" t="n">
-        <v>10</v>
-      </c>
-      <c r="D14" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="F14" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="H14" s="28" t="n">
-        <v>75000</v>
-      </c>
-      <c r="I14" s="29" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="J14" s="29" t="n">
-        <v>40</v>
-      </c>
-      <c r="K14" s="29" t="n">
-        <v>1612.5</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="26" t="n">
-        <v>11</v>
-      </c>
-      <c r="D15" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="E15" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="F15" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="H15" s="28" t="n">
-        <v>125000</v>
-      </c>
-      <c r="I15" s="29" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="J15" s="29" t="n">
-        <v>70</v>
-      </c>
-      <c r="K15" s="29" t="n">
-        <v>2687.5</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="26" t="n">
-        <v>12</v>
-      </c>
-      <c r="D16" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="F16" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="H16" s="28" t="n">
-        <v>200000</v>
-      </c>
-      <c r="I16" s="29" t="n">
-        <v>100</v>
-      </c>
-      <c r="J16" s="29" t="n">
-        <v>110</v>
-      </c>
-      <c r="K16" s="29" t="n">
-        <v>2540</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="26" t="n">
-        <v>13</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="E17" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="F17" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="H17" s="28" t="n">
-        <v>200000</v>
-      </c>
-      <c r="I17" s="29" t="n">
-        <v>100</v>
-      </c>
-      <c r="J17" s="29" t="n">
-        <v>110</v>
-      </c>
-      <c r="K17" s="29" t="n">
-        <v>2540</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="26" t="n">
-        <v>14</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="E18" s="26" t="s">
+      <c r="I25" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="K25" s="10" t="n">
+        <v>2712.8</v>
+      </c>
+      <c r="L25" s="7" t="s">
         <v>125</v>
-      </c>
-      <c r="F18" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="H18" s="28" t="n">
-        <v>180000</v>
-      </c>
-      <c r="I18" s="29" t="n">
-        <v>299.7</v>
-      </c>
-      <c r="J18" s="29" t="n">
-        <v>310.5</v>
-      </c>
-      <c r="K18" s="29" t="n">
-        <v>12600</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="26" t="n">
-        <v>15</v>
-      </c>
-      <c r="D19" s="26" t="s">
-        <v>126</v>
-      </c>
-      <c r="E19" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="F19" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="H19" s="28" t="n">
-        <v>30000</v>
-      </c>
-      <c r="I19" s="29" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="J19" s="29" t="n">
-        <v>15</v>
-      </c>
-      <c r="K19" s="29" t="n">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="26" t="n">
-        <v>16</v>
-      </c>
-      <c r="D20" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="E20" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="F20" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="H20" s="28" t="n">
-        <v>51200</v>
-      </c>
-      <c r="I20" s="29" t="n">
-        <v>235.52</v>
-      </c>
-      <c r="J20" s="29" t="n">
-        <v>250</v>
-      </c>
-      <c r="K20" s="29" t="n">
-        <v>8120.32</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="F21" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H21" s="28" t="n">
-        <v>19152</v>
-      </c>
-      <c r="I21" s="29" t="n">
-        <v>11299.68</v>
-      </c>
-      <c r="J21" s="29" t="n">
-        <v>11688.8</v>
-      </c>
-      <c r="K21" s="29" t="n">
-        <v>19918.08</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="D22" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="F22" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="H22" s="28" t="n">
-        <v>2016</v>
-      </c>
-      <c r="I22" s="29" t="n">
-        <v>1149.12</v>
-      </c>
-      <c r="J22" s="29" t="n">
-        <v>1219.04</v>
-      </c>
-      <c r="K22" s="29" t="n">
-        <v>5140.8</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="B23" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="C23" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="F23" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="H23" s="28" t="n">
-        <v>33600</v>
-      </c>
-      <c r="I23" s="29" t="n">
-        <v>856.8</v>
-      </c>
-      <c r="J23" s="29" t="n">
-        <v>1134</v>
-      </c>
-      <c r="K23" s="29" t="n">
-        <v>16836.96</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="B24" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="C24" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="D24" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="F24" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="H24" s="28" t="n">
-        <v>2160</v>
-      </c>
-      <c r="I24" s="29" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="J24" s="29" t="n">
-        <v>84.12</v>
-      </c>
-      <c r="K24" s="29" t="n">
-        <v>1280.88</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="B25" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="E25" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="F25" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="H25" s="28" t="n">
-        <v>8000</v>
-      </c>
-      <c r="I25" s="29" t="n">
-        <v>48</v>
-      </c>
-      <c r="J25" s="29" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="K25" s="29" t="n">
-        <v>2712.8</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2871,7 +3239,7 @@
       <c r="E26" s="20"/>
       <c r="F26" s="20"/>
       <c r="G26" s="21" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="H26" s="22" t="n">
         <f aca="false">SUM(H2:H25)</f>
@@ -2889,9 +3257,10 @@
         <f aca="false">SUM(K2:K25)</f>
         <v>119371.08</v>
       </c>
+      <c r="L26" s="20"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K25"/>
+  <autoFilter ref="A1:L25"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2903,12 +3272,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
@@ -2918,205 +3287,194 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="30" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="C3" s="30" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="B6" s="31" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="C9" s="32" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="32" t="s">
-        <v>59</v>
+        <v>174</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="32" t="s">
+        <v>179</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>180</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="32" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="32" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="32" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="32" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="B16" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="C16" s="32" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>153</v>
+        <v>190</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -3130,97 +3488,105 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="110"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="112"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3"/>
-      <c r="B11" s="35"/>
-    </row>
-    <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="36" t="s">
-        <v>198</v>
-      </c>
-      <c r="B12" s="37" t="s">
-        <v>199</v>
+      <c r="A11" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3"/>
+      <c r="B12" s="35"/>
+    </row>
+    <row r="13" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="B13" s="37" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>

--- a/output/HS_Code_Summary_Sonavox_Technology_CZ_TECGO26080029.xlsx
+++ b/output/HS_Code_Summary_Sonavox_Technology_CZ_TECGO26080029.xlsx
@@ -9,7 +9,7 @@
   </bookViews>
   <sheets>
     <sheet name="HS Summary" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Chybějící HS kódy" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Doplněné HS kódy" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Line items" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Poznámky &amp; flagy" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Zdroje" sheetId="5" state="visible" r:id="rId7"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="242">
   <si>
     <t xml:space="preserve">HS CODE SUMMARY – Sonavox Technology CZ s.r.o.</t>
   </si>
@@ -110,10 +110,22 @@
     <t xml:space="preserve">51 palet / 51,40 CBM / brutto 24 133 kg (souhlasí s FCR i SMGS)</t>
   </si>
   <si>
-    <t xml:space="preserve">CHYBĚJÍCÍ HS KÓDY:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 položky bez kódu v podkladech (9 360,00 EUR) – viz list „Chybějící HS kódy“</t>
+    <t xml:space="preserve">Doplněné HS kódy:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 položky doplnil klient 12.08.2026 – viz list „Doplněné HS kódy“ (u Spring nut jen 6 míst, nutno doplnit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBAM:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prohlášení de minimis Y137 (do 50 t/rok) ze dne 12.08.2026, podepsala Ing. Michaela Ryan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTIDUMPING:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEVYŘEŠEN – prohlášení Y137 se týká CBAM, nikoli antidumpingu. Viz Poznámky.</t>
   </si>
   <si>
     <t xml:space="preserve">Odesílatel / Sender</t>
@@ -173,10 +185,10 @@
     <t xml:space="preserve">8518900000</t>
   </si>
   <si>
-    <t xml:space="preserve">Ocelová deska (front plate) – součást autoreproduktoru; Středící membrána (spider) – naimpregnovaná textilie, součást autoreproduktoru; Membrána s vlnkou (cone) – membrána elektrodynamického reproduktoru; Kontakt / vývod (terminal) – část autoreproduktoru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Části a součásti reproduktorů, DK 00 dle předchozích celních prohlášení.</t>
+    <t xml:space="preserve">Ocelová deska (front plate) – součást autoreproduktoru; Středící membrána (spider) – naimpregnovaná textilie, součást autoreproduktoru; Membrána s vlnkou (cone) – membrána elektrodynamického reproduktoru; Kontakt / vývod (terminal) – část autoreproduktoru; Vodotěsná membrána – část autoreproduktoru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Části a součásti reproduktorů, DK 00 dle předchozích celních prohlášení. Zahrnuje i Waterproof membrane dle sdělení klienta z 12.08.2026.</t>
   </si>
   <si>
     <t xml:space="preserve">3926909790</t>
@@ -194,337 +206,382 @@
     <t xml:space="preserve">Matice / vložka (nut, insert) – závitové zboží ze železa nebo oceli</t>
   </si>
   <si>
-    <t xml:space="preserve">ANO</t>
+    <t xml:space="preserve">ANO – Y137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANO – 90,2 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antidumping potvrzen výpočtem v Helios: 3,7 % clo + 86,5 % AD = 90,2 %, základ 304 416 Kč → 274 584 Kč. CBAM pokryt prohlášením Y137. ROZPOR: spring nut má dle klienta 7318 16 (matice, bez AD) – viz Poznámky.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7413000090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kabelový svazek – splétaná lanka z mědi, elektricky neizolovaná</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Splétaná lanka z mědi, neizolovaná, DK 90 dle předchozího celního prohlášení.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">731816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pružná matice (spring nut) – matice ze železa nebo oceli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matice ze železa/oceli. Kód 7318 16 NENÍ v seznamu nař. (EU) 2022/191, antidumping se tedy neuplatní. POZOR: kód je jen 6místný, nutno doplnit na 10.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mezisoučet – Suzhou Sonavox International Trading Co., Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suzhou Sonavox Electronics Co., Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CZ20260725-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magnetický obvod (ceramics circle) – feritové jádro (nezmagnetované), součást autoreproduktoru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8518210000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reproduktor (autoreproduktor), jediný v jedné skříni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kompletní autoreproduktor, jediný v jedné skříni.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mezisoučet – Suzhou Sonavox Electronics Co., Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suzhou Yanlong Electronic Product Co., Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CZ20260725-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Membrána s vlnkou (cone) – membrána elektrodynamického reproduktoru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mezisoučet – Suzhou Yanlong Electronic Product Co., Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CELKEM ZÁSILKA / TOTAL SHIPMENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kontrola / cross-check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ze souhrnu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z dokladů</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rozdíl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Množství celkem vs. součet faktur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Čistá hmotnost celkem (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hrubá hmotnost celkem (kg) vs. FCR/SMGS 24 133 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Celní hodnota celkem (EUR) vs. součet faktur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS KÓDY DODATEČNĚ DOPLNĚNÉ KLIENTEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyto dvě položky neměly HS kód v žádném původním podkladu. Kódy dodala Alice Knápková (Sonavox Technology CZ) e-mailem dne 12.08.2026 – viz sloupec Zdroj.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Odesílatel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pol. č.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Popis dle faktury (EN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Čistá hm. (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hrubá hm. (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HS kód od klienta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stav kódu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zdroj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J2-10X002-0001-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterproof membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK – úplný 10místný kód</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e-mail Alice Knápková, 12.08.2026: „Waterproof membrane  8518900000“</t>
+  </si>
+  <si>
+    <t xml:space="preserve">029A-000004-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spring nut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEÚPLNÝ – jen 6 míst, nutno doplnit na 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e-mail Alice Knápková, 12.08.2026: „029A-000004-CZ  HS 731816“</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invoice No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description of Goods (EN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity (pcs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net weight (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross weight (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customs value (EUR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zdroj HS kódu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">010-KD1622S-3.8A-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voice coil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e-mail SONAVOX HS KODY: „Voice Coil / Kmitací cívka – HS 85045000 00“ (ZISZ 30-0292-2016)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">040-62E4-CR-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Front plate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ocelová deska (front plate) – součást autoreproduktoru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">předchozí celní prohlášení Sonavox: „Front plate – deska“, CN 8518 90 00 DK 00 (POZOR: e-mail uvádí ...90 – rozpor)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">040-80I6-CRB-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">040-54D3-CR-1-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021-100F00-9-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Středící membrána (spider) – naimpregnovaná textilie, součást autoreproduktoru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e-mail SONAVOX HS KODY + předchozí celní prohlášení: „Spider – 8518 9000 00“</t>
+  </si>
+  <si>
+    <t xml:space="preserve">021-80E15-3-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140-35D14-44XP1-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e-mail SONAVOX HS KODY + předchozí celní prohlášení: „Cone – HS 85189000 00“</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181-35113-1SN-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kontakt / vývod (terminal) – část autoreproduktoru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">předchozí celní prohlášení Sonavox: „terminal – části reproduktorů“, CN 8518 90 00 DK 00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181-35113-2SN-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181-40133-1SN-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">181-40133-2SN-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-630H10-15H-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gasket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plastové těsnění (gasket) – ostatní výrobky z plastů</t>
+  </si>
+  <si>
+    <t xml:space="preserve">předchozí celní prohlášení Sonavox: „Gassket – plastové těsnění“, CN 3926 90 97 DK 90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142-40X25-25D-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JK-65425-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gauge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plastový kalibr (gauge) – montážní přípravek, ostatní výrobky z plastů</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e-mail SONAVOX HS KODY + předchozí celní prohlášení: „Gauge – 3926 9097 90“</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JK-35113-01-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">029-2513-AL-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e-mail SONAVOX HS KODY: „Insert (nut) – 7318159519“ (POZOR: materiál dílu neověřen – viz Poznámky)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">008-XH-2Y-DK-6-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">předchozí celní prohlášení Sonavox: „harness – kabelový svazek“, CN 7413 00 00 DK 90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vodotěsná membrána – část autoreproduktoru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e-mail Alice Knápková (Sonavox Technology CZ), 12.08.2026: „Waterproof membrane – 8518900000“</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e-mail Alice Knápková (Sonavox Technology CZ), 12.08.2026: „029A-000004-CZ – HS 731816“ (POZOR: jen 6 míst, nutno doplnit na 10 – 7318 16 má šest podpoložek)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212-8075-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceramics circle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e-mail SONAVOX HS KODY: „CERAMICS CIRCLE / magnetický obvod – 8518900000“</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IM-50196-AUDICZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Car Speaker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e-mail SONAVOX HS KODY + předchozí celní prohlášení: „SPEAKER / reproduktor – 8518210000“, CN 8518 21 00 DK 00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140-80I27-42X-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140-80E30-58X-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140-40E17-72XC-CZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CELKEM / TOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POZNÁMKY, UPOZORNĚNÍ A NESROVNALOSTI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priorita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Téma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Popis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KRITICKÉ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prohlášení Y137 řeší CBAM, NIKOLI antidumping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Na dotaz k antidumpingu u položky 7318 15 95 19 zaslal klient dne 12.08.2026 prohlášení podepsané Ing. Michaelou Ryan: „Sonavox Technology CZ s.r.o. uplatňuje výjimku de minimis – za kalendářní rok naše dovozy nepřesáhnou kumulativně 50 tun čisté hmotnosti (kód Y137)“. Kód Y137 je však kód CBAM (uhlíkové vyrovnávací opatření), NE antidumping. Antidumpingové clo dle nař. (EU) 2022/191 žádnou obdobnou výjimku de minimis nemá. Clo 274 584 Kč tedy tímto prohlášením NEODPADÁ. NUTNO KLIENTOVI VYSVĚTLIT A ZNOVU VYŽÁDAT NÁZEV A ADRESU ČÍNSKÉHO VÝROBCE.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rozpor 7318 16 vs. 7318 15 95 – možná úspora 274 584 Kč</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klient dne 12.08.2026 zařadil Spring nut (029A-000004-CZ) pod HS 7318 16, tedy pod MATICE. Položka 14 „Nut“ (029-2513-AL-CZ) je přitom dle tabulky SONAVOX pod 7318 15 95 19, tedy pod ŠROUBY A SVORNÍKY. Pokud je i díl 029-2513-AL-CZ maticí, patří rovněž pod 7318 16 – a ten v seznamu nař. (EU) 2022/191 NENÍ, takže by antidumping zcela odpadl. Rozdíl činí 274 584 Kč. NUTNO S KLIENTEM VYJASNIT, PROČ JSOU DVA PODOBNÉ DÍLY V RŮZNÝCH POLOŽKÁCH.</t>
   </si>
   <si>
     <t xml:space="preserve">K OVĚŘENÍ</t>
   </si>
   <si>
-    <t xml:space="preserve">CBAM platí i pro hliníkovou variantu (7616). Antidumping závisí na materiálu a druhu dílu – viz list Poznámky.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7413000090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kabelový svazek – splétaná lanka z mědi, elektricky neizolovaná</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Splétaná lanka z mědi, neizolovaná, DK 90 dle předchozího celního prohlášení.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHYBÍ – VYŽÁDAT OD KLIENTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vodotěsná membrána (dle faktury „Waterproof membrane“ – český popis není k dispozici)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NENÍ V PODKLADECH – v e-mailu SONAVOX ani v předchozích celních prohlášeních tato položka není</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pružná matice (dle faktury „Spring nut“ – český popis není k dispozici)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mezisoučet – Suzhou Sonavox International Trading Co., Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suzhou Sonavox Electronics Co., Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CZ20260725-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magnetický obvod (ceramics circle) – feritové jádro (nezmagnetované), součást autoreproduktoru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8518210000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reproduktor (autoreproduktor), jediný v jedné skříni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kompletní autoreproduktor, jediný v jedné skříni.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mezisoučet – Suzhou Sonavox Electronics Co., Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suzhou Yanlong Electronic Product Co., Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CZ20260725-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Membrána s vlnkou (cone) – membrána elektrodynamického reproduktoru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mezisoučet – Suzhou Yanlong Electronic Product Co., Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CELKEM ZÁSILKA / TOTAL SHIPMENT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kontrola / cross-check</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ze souhrnu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z dokladů</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rozdíl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Množství celkem vs. součet faktur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Čistá hmotnost celkem (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hrubá hmotnost celkem (kg) vs. FCR/SMGS 24 133 kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Celní hodnota celkem (EUR) vs. součet faktur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POLOŽKY BEZ HS KÓDU – NUTNO VYŽÁDAT OD KLIENTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyto položky nemají HS kód v žádném podkladu – ani v e-mailu „SONAVOX HS KODY“, ani v předchozích celních prohlášeních Sonavox. Kód nelze doplnit vlastním odvozením; musí ho poskytnout klient.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Odesílatel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pol. č.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Part Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Popis dle faktury (EN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Čistá hm. (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hrubá hm. (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HS kód – DOPLNÍ KLIENT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J2-10X002-0001-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterproof membrane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">029A-000004-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spring nut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CELKEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invoice No.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description of Goods (EN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity (pcs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net weight (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gross weight (kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customs value (EUR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zdroj HS kódu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">010-KD1622S-3.8A-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voice coil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e-mail SONAVOX HS KODY: „Voice Coil / Kmitací cívka – HS 85045000 00“ (ZISZ 30-0292-2016)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">040-62E4-CR-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Front plate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ocelová deska (front plate) – součást autoreproduktoru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">předchozí celní prohlášení Sonavox: „Front plate – deska“, CN 8518 90 00 DK 00 (POZOR: e-mail uvádí ...90 – rozpor)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">040-80I6-CRB-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">040-54D3-CR-1-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021-100F00-9-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Středící membrána (spider) – naimpregnovaná textilie, součást autoreproduktoru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e-mail SONAVOX HS KODY + předchozí celní prohlášení: „Spider – 8518 9000 00“</t>
-  </si>
-  <si>
-    <t xml:space="preserve">021-80E15-3-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140-35D14-44XP1-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e-mail SONAVOX HS KODY + předchozí celní prohlášení: „Cone – HS 85189000 00“</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181-35113-1SN-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terminal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kontakt / vývod (terminal) – část autoreproduktoru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">předchozí celní prohlášení Sonavox: „terminal – části reproduktorů“, CN 8518 90 00 DK 00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181-35113-2SN-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181-40133-1SN-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">181-40133-2SN-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142-630H10-15H-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gasket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plastové těsnění (gasket) – ostatní výrobky z plastů</t>
-  </si>
-  <si>
-    <t xml:space="preserve">předchozí celní prohlášení Sonavox: „Gassket – plastové těsnění“, CN 3926 90 97 DK 90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142-40X25-25D-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JK-65425-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gauge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plastový kalibr (gauge) – montážní přípravek, ostatní výrobky z plastů</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e-mail SONAVOX HS KODY + předchozí celní prohlášení: „Gauge – 3926 9097 90“</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JK-35113-01-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">029-2513-AL-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e-mail SONAVOX HS KODY: „Insert (nut) – 7318159519“ (POZOR: materiál dílu neověřen – viz Poznámky)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">008-XH-2Y-DK-6-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">předchozí celní prohlášení Sonavox: „harness – kabelový svazek“, CN 7413 00 00 DK 90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212-8075-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ceramics circle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e-mail SONAVOX HS KODY: „CERAMICS CIRCLE / magnetický obvod – 8518900000“</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IM-50196-AUDICZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Car Speaker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e-mail SONAVOX HS KODY + předchozí celní prohlášení: „SPEAKER / reproduktor – 8518210000“, CN 8518 21 00 DK 00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140-80I27-42X-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140-80E30-58X-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140-40E17-72XC-CZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CELKEM / TOTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POZNÁMKY, UPOZORNĚNÍ A NESROVNALOSTI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priorita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Téma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Popis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KRITICKÉ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dvě položky bez HS kódu – nelze proclít</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waterproof membrane J2-10X002-0001-CZ (210 000 ks, 8 820,00 EUR) a Spring nut 029A-000004-CZ (30 000 ks, 540,00 EUR), obě z faktury CZ20260725. Ani jedna není v e-mailu „SONAVOX HS KODY“ ani v předchozích celních prohlášeních. Kódy NEBYLY doplněny vlastním odvozením – musí je poskytnout klient. Detail na listu „Chybějící HS kódy“.</t>
+    <t xml:space="preserve">Spring nut – kód je jen 6místný</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klient uvedl „HS 731816“, tedy pouze 6 míst. Do celního prohlášení je nutný 10místný kód; podpoložka 7318 16 se dále dělí podle typu matice a vnitřního průměru. Nutno vyžádat doplnění.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VYŘEŠENO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waterproof membrane – kód doplněn klientem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klient dne 12.08.2026 zařadil J2-10X002-0001-CZ (210 000 ks, 8 820,00 EUR) pod 8518 90 00 00, tedy jako část reproduktoru. Kód je úplný a odpovídá DK 00 používanému u ostatních částí. Položka je proto sloučena do řádku 8518 90 00 00.</t>
   </si>
   <si>
     <t xml:space="preserve">Preferenční věta / preferenční původ (COO)</t>
@@ -539,16 +596,22 @@
     <t xml:space="preserve">Všechny tři faktury i packing listy uvádějí pouze „Terms of Payment: FOB“ – BEZ přístavu / jmenovaného místa. Navíc FOB je dle Incoterms 2020 určen jen pro námořní a vnitrozemskou vodní přepravu, ale zásilka jde ŽELEZNICÍ (Zhengzhou/Putian → Malaszewicze → CZ); správný termín je FCA s uvedeným místem. FCR je „freight collect“, takže bez určení dodacího místa nelze spolehlivě určit, zda se do celní hodnoty připočítává dopravné do hranice EU.</t>
   </si>
   <si>
-    <t xml:space="preserve">Antidumping u matic – závisí na materiálu i na druhu dílu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Položka 14 (Nut, 029-2513-AL-CZ, 180 000 ks, 12 600,00 EUR) má dle e-mailu SONAVOX kód 7318 15 95 19. Tři možné scénáře: (a) HLINÍK → 7616 10 00, clo cca 6 %, BEZ antidumpingu; (b) OCELOVÁ MATICE → 7318 16, clo cca 3,7 %, BEZ antidumpingu; (c) OCELOVÝ ŠROUB / VLOŽKA → ex 7318 15 95, clo 3,7 % + ANTIDUMPING 22,1–86,5 %. Nař. (EU) 2022/191 se vztahuje na vruty, samořezné šrouby, ostatní šrouby a svorníky s hlavou a podložky (7318 12 90, 7318 14 91, 7318 14 99, 7318 15 58, 7318 15 68, 7318 15 82, 7318 15 88, ex 7318 15 95, ex 7318 21 00, ex 7318 22 00) – kód 7318 16 pro MATICE v seznamu NENÍ. Bez jména čínského výrobce se uplatní zbytková sazba 86,5 %. NUTNO ZJISTIT MATERIÁL, DRUH DÍLU A VÝROBCE.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CBAM – platí u matic v každé variantě</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Položka 14 (180 000 ks, čistá hmotnost 299,70 kg) spadá do přílohy I nařízení CBAM bez ohledu na výsledek otázky materiálu – kapitola 73 (železo a ocel) i kapitola 76 (hliník) jsou v příloze I. Nutno zahrnout do čtvrtletního CBAM hlášení. Pokud bude Spring nut zařazen do stejné kapitoly, platí totéž i pro něj. Ostatní položky zásilky (kap. 39, 85) do CBAM nespadají.</t>
+    <t xml:space="preserve">Antidumping u matic – vyčísleno 274 584 Kč</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Položka 14 (Nut, 029-2513-AL-CZ, 180 000 ks, 12 600,00 EUR) pod kódem 7318 15 95 19. Výpočet v Helios: druh A00, základ 304 416 Kč, sazba 90,2 % (= 3,7 % clo + 86,5 % antidumping), částka 274 584 Kč. Sazba 86,5 % je ZBYTKOVÁ pro neznámého/nespolupracujícího výrobce; s názvem a adresou čínského výrobce lze získat doplňkový kód TARIC se sazbou 22,1–48,8 % (clo celkem 25,8–52,5 %, tj. 78 539–159 818 Kč) nebo 39,6 % pro spolupracující výrobce (131 812 Kč). Možná úspora až cca 196 000 Kč. Tři možné scénáře: (a) HLINÍK → 7616 10 00, clo cca 6 %, BEZ antidumpingu; (b) OCELOVÁ MATICE → 7318 16, clo cca 3,7 %, BEZ antidumpingu; (c) OCELOVÝ ŠROUB / VLOŽKA → ex 7318 15 95, clo 3,7 % + ANTIDUMPING 22,1–86,5 %. Nař. (EU) 2022/191 se vztahuje na vruty, samořezné šrouby, ostatní šrouby a svorníky s hlavou a podložky (7318 12 90, 7318 14 91, 7318 14 99, 7318 15 58, 7318 15 68, 7318 15 82, 7318 15 88, ex 7318 15 95, ex 7318 21 00, ex 7318 22 00) – kód 7318 16 pro MATICE v seznamu NENÍ. Bez jména čínského výrobce se uplatní zbytková sazba 86,5 %. NUTNO ZJISTIT MATERIÁL, DRUH DÍLU A VÝROBCE.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBAM – prohlášení de minimis Y137 doloženo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Položky 14 a 15 (7318 15 95 19 a 7318 16, celkem 312,30 kg čisté hmotnosti) spadají do přílohy I nařízení CBAM. Klient doložil dne 12.08.2026 podepsané prohlášení, že dovozy Sonavox Technology CZ s.r.o. nepřesáhnou za kalendářní rok kumulativně 50 tun čisté hmotnosti – kód Y137 (do 50 t ročně). V celním prohlášení se tedy u těchto položek uvede Y137. POZOR: platnost je vázána na kumulativní roční objem – při dalších dovozech je nutno sledovat součet. Ostatní položky zásilky (kap. 39, 85) do CBAM nespadají.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBAM registr příjemců nebyl k dispozici</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referenční soubor reference/CBAM_receivers_CZ.xlsx (list List1) není v repozitáři k dispozici, nebylo proto možné ověřit zápis příjemce Sonavox Technology CZ s.r.o. (IČO 19670338, DIČ CZ19670338) v registru ani porovnat deklarovaný kód Y137 se záznamem. Doporučeno ověřit a případně příjemce do registru doplnit.</t>
   </si>
   <si>
     <t xml:space="preserve">ROZPOR</t>
@@ -762,7 +825,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -783,12 +846,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4E4"/>
-        <bgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
         <bgColor rgb="FFF2F2F2"/>
       </patternFill>
@@ -801,8 +858,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFFCE4E4"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -855,7 +912,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -900,24 +957,20 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -936,40 +989,32 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="166" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="167" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -980,7 +1025,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1000,11 +1045,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1017,19 +1062,11 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF1F4E79"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4E4"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1045,14 +1082,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC00000"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1305,7 +1334,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
@@ -1431,658 +1460,632 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B17" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="6" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="B18" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E18" s="6" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="B20" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="C20" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="D20" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="E20" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J18" s="6" t="s">
+      <c r="F20" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="K18" s="6" t="s">
+      <c r="G20" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="L18" s="6" t="s">
+      <c r="H20" s="6" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+      <c r="I20" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="J20" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="K20" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="L20" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A19,'Line items'!$F$2:$F$25,$C19)</f>
-        <v>65000</v>
-      </c>
-      <c r="F19" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A19,'Line items'!$F$2:$F$25,$C19)</f>
-        <v>86.5</v>
-      </c>
-      <c r="G19" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A19,'Line items'!$F$2:$F$25,$C19)</f>
-        <v>216.33</v>
-      </c>
-      <c r="H19" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A19,'Line items'!$F$2:$F$25,$C19)</f>
-        <v>9841</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="L19" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A20,'Line items'!$F$2:$F$25,$C20)</f>
-        <v>778000</v>
-      </c>
-      <c r="F20" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A20,'Line items'!$F$2:$F$25,$C20)</f>
-        <v>8806.4</v>
-      </c>
-      <c r="G20" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A20,'Line items'!$F$2:$F$25,$C20)</f>
-        <v>8990.91</v>
-      </c>
-      <c r="H20" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A20,'Line items'!$F$2:$F$25,$C20)</f>
-        <v>32182.14</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E21" s="9" t="n">
         <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A21,'Line items'!$F$2:$F$25,$C21)</f>
-        <v>9960</v>
+        <v>65000</v>
       </c>
       <c r="F21" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A21,'Line items'!$F$2:$F$25,$C21)</f>
-        <v>103.09</v>
+        <v>86.5</v>
       </c>
       <c r="G21" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A21,'Line items'!$F$2:$F$25,$C21)</f>
-        <v>128</v>
+        <v>216.33</v>
       </c>
       <c r="H21" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A21,'Line items'!$F$2:$F$25,$C21)</f>
-        <v>1378.1</v>
+        <v>9841</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>22</v>
       </c>
       <c r="J21" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="K21" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="L21" s="7" t="s">
+      <c r="B22" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="12" t="s">
+      <c r="E22" s="9" t="n">
+        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A22,'Line items'!$F$2:$F$25,$C22)</f>
+        <v>988000</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A22,'Line items'!$F$2:$F$25,$C22)</f>
+        <v>8836.64</v>
+      </c>
+      <c r="G22" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A22,'Line items'!$F$2:$F$25,$C22)</f>
+        <v>9030.91</v>
+      </c>
+      <c r="H22" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A22,'Line items'!$F$2:$F$25,$C22)</f>
+        <v>41002.14</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="7" t="s">
         <v>53</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E22" s="13" t="n">
-        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A22,'Line items'!$F$2:$F$25,$C22)</f>
-        <v>180000</v>
-      </c>
-      <c r="F22" s="14" t="n">
-        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A22,'Line items'!$F$2:$F$25,$C22)</f>
-        <v>299.7</v>
-      </c>
-      <c r="G22" s="14" t="n">
-        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A22,'Line items'!$F$2:$F$25,$C22)</f>
-        <v>310.5</v>
-      </c>
-      <c r="H22" s="14" t="n">
-        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A22,'Line items'!$F$2:$F$25,$C22)</f>
-        <v>12600</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J22" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="K22" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="L22" s="11" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E23" s="9" t="n">
         <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A23,'Line items'!$F$2:$F$25,$C23)</f>
-        <v>51200</v>
+        <v>9960</v>
       </c>
       <c r="F23" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A23,'Line items'!$F$2:$F$25,$C23)</f>
-        <v>235.52</v>
+        <v>103.09</v>
       </c>
       <c r="G23" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A23,'Line items'!$F$2:$F$25,$C23)</f>
-        <v>250</v>
+        <v>128</v>
       </c>
       <c r="H23" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A23,'Line items'!$F$2:$F$25,$C23)</f>
-        <v>8120.32</v>
+        <v>1378.1</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>22</v>
       </c>
       <c r="J23" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="K23" s="7" t="s">
+      <c r="B24" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A24,'Line items'!$F$2:$F$25,$C24)</f>
+        <v>180000</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A24,'Line items'!$F$2:$F$25,$C24)</f>
+        <v>299.7</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A24,'Line items'!$F$2:$F$25,$C24)</f>
+        <v>310.5</v>
+      </c>
+      <c r="H24" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A24,'Line items'!$F$2:$F$25,$C24)</f>
+        <v>12600</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L23" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D24" s="11" t="s">
+      <c r="B25" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E24" s="13" t="n">
-        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A24,'Line items'!$D$2:$D$25,"J2-10X002-0001-CZ")</f>
-        <v>210000</v>
-      </c>
-      <c r="F24" s="14" t="n">
-        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A24,'Line items'!$D$2:$D$25,"J2-10X002-0001-CZ")</f>
-        <v>30.24</v>
-      </c>
-      <c r="G24" s="14" t="n">
-        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A24,'Line items'!$D$2:$D$25,"J2-10X002-0001-CZ")</f>
-        <v>40</v>
-      </c>
-      <c r="H24" s="14" t="n">
-        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A24,'Line items'!$D$2:$D$25,"J2-10X002-0001-CZ")</f>
-        <v>8820</v>
-      </c>
-      <c r="I24" s="11" t="s">
+      <c r="D25" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A25,'Line items'!$F$2:$F$25,$C25)</f>
+        <v>51200</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A25,'Line items'!$F$2:$F$25,$C25)</f>
+        <v>235.52</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A25,'Line items'!$F$2:$F$25,$C25)</f>
+        <v>250</v>
+      </c>
+      <c r="H25" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A25,'Line items'!$F$2:$F$25,$C25)</f>
+        <v>8120.32</v>
+      </c>
+      <c r="I25" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J24" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="K24" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="L24" s="11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D25" s="11" t="s">
+      <c r="J25" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E25" s="13" t="n">
-        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A25,'Line items'!$D$2:$D$25,"029A-000004-CZ")</f>
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A26,'Line items'!$F$2:$F$25,$C26)</f>
         <v>30000</v>
       </c>
-      <c r="F25" s="14" t="n">
-        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A25,'Line items'!$D$2:$D$25,"029A-000004-CZ")</f>
+      <c r="F26" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A26,'Line items'!$F$2:$F$25,$C26)</f>
         <v>12.6</v>
       </c>
-      <c r="G25" s="14" t="n">
-        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A25,'Line items'!$D$2:$D$25,"029A-000004-CZ")</f>
+      <c r="G26" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A26,'Line items'!$F$2:$F$25,$C26)</f>
         <v>15</v>
       </c>
-      <c r="H25" s="14" t="n">
-        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A25,'Line items'!$D$2:$D$25,"029A-000004-CZ")</f>
+      <c r="H26" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A26,'Line items'!$F$2:$F$25,$C26)</f>
         <v>540</v>
       </c>
-      <c r="I25" s="11" t="s">
+      <c r="I26" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J25" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="K25" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="L25" s="11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="E26" s="18" t="n">
-        <f aca="false">SUM(E19:E25)</f>
+      <c r="J26" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <f aca="false">SUM(E21:E26)</f>
         <v>1324160</v>
       </c>
-      <c r="F26" s="19" t="n">
-        <f aca="false">SUM(F19:F25)</f>
+      <c r="F27" s="14" t="n">
+        <f aca="false">SUM(F21:F26)</f>
         <v>9574.05</v>
       </c>
-      <c r="G26" s="19" t="n">
-        <f aca="false">SUM(G19:G25)</f>
+      <c r="G27" s="14" t="n">
+        <f aca="false">SUM(G21:G26)</f>
         <v>9950.74</v>
       </c>
-      <c r="H26" s="19" t="n">
-        <f aca="false">SUM(H19:H25)</f>
+      <c r="H27" s="14" t="n">
+        <f aca="false">SUM(H21:H26)</f>
         <v>73481.56</v>
       </c>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-    </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E27" s="9" t="n">
-        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A27,'Line items'!$F$2:$F$25,$C27)</f>
-        <v>19152</v>
-      </c>
-      <c r="F27" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A27,'Line items'!$F$2:$F$25,$C27)</f>
-        <v>11299.68</v>
-      </c>
-      <c r="G27" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A27,'Line items'!$F$2:$F$25,$C27)</f>
-        <v>11688.8</v>
-      </c>
-      <c r="H27" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A27,'Line items'!$F$2:$F$25,$C27)</f>
-        <v>19918.08</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="L27" s="7" t="s">
-        <v>49</v>
-      </c>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E28" s="9" t="n">
         <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A28,'Line items'!$F$2:$F$25,$C28)</f>
-        <v>2016</v>
+        <v>19152</v>
       </c>
       <c r="F28" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A28,'Line items'!$F$2:$F$25,$C28)</f>
-        <v>1149.12</v>
+        <v>11299.68</v>
       </c>
       <c r="G28" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A28,'Line items'!$F$2:$F$25,$C28)</f>
-        <v>1219.04</v>
+        <v>11688.8</v>
       </c>
       <c r="H28" s="10" t="n">
         <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A28,'Line items'!$F$2:$F$25,$C28)</f>
-        <v>5140.8</v>
+        <v>19918.08</v>
       </c>
       <c r="I28" s="7" t="s">
         <v>22</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="16"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E29" s="18" t="n">
-        <f aca="false">SUM(E27:E28)</f>
+      <c r="D29" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A29,'Line items'!$F$2:$F$25,$C29)</f>
+        <v>2016</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A29,'Line items'!$F$2:$F$25,$C29)</f>
+        <v>1149.12</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A29,'Line items'!$F$2:$F$25,$C29)</f>
+        <v>1219.04</v>
+      </c>
+      <c r="H29" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A29,'Line items'!$F$2:$F$25,$C29)</f>
+        <v>5140.8</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E30" s="13" t="n">
+        <f aca="false">SUM(E28:E29)</f>
         <v>21168</v>
       </c>
-      <c r="F29" s="19" t="n">
-        <f aca="false">SUM(F27:F28)</f>
+      <c r="F30" s="14" t="n">
+        <f aca="false">SUM(F28:F29)</f>
         <v>12448.8</v>
       </c>
-      <c r="G29" s="19" t="n">
-        <f aca="false">SUM(G27:G28)</f>
+      <c r="G30" s="14" t="n">
+        <f aca="false">SUM(G28:G29)</f>
         <v>12907.84</v>
       </c>
-      <c r="H29" s="19" t="n">
-        <f aca="false">SUM(H27:H28)</f>
+      <c r="H30" s="14" t="n">
+        <f aca="false">SUM(H28:H29)</f>
         <v>25058.88</v>
       </c>
-      <c r="I29" s="16"/>
-      <c r="J29" s="16"/>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-    </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E30" s="9" t="n">
-        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A30,'Line items'!$F$2:$F$25,$C30)</f>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+    </row>
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <f aca="false">SUMIFS('Line items'!H$2:H$25,'Line items'!$A$2:$A$25,$A31,'Line items'!$F$2:$F$25,$C31)</f>
         <v>43760</v>
       </c>
-      <c r="F30" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A30,'Line items'!$F$2:$F$25,$C30)</f>
+      <c r="F31" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!I$2:I$25,'Line items'!$A$2:$A$25,$A31,'Line items'!$F$2:$F$25,$C31)</f>
         <v>957</v>
       </c>
-      <c r="G30" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A30,'Line items'!$F$2:$F$25,$C30)</f>
+      <c r="G31" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!J$2:J$25,'Line items'!$A$2:$A$25,$A31,'Line items'!$F$2:$F$25,$C31)</f>
         <v>1274.42</v>
       </c>
-      <c r="H30" s="10" t="n">
-        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A30,'Line items'!$F$2:$F$25,$C30)</f>
+      <c r="H31" s="10" t="n">
+        <f aca="false">SUMIFS('Line items'!K$2:K$25,'Line items'!$A$2:$A$25,$A31,'Line items'!$F$2:$F$25,$C31)</f>
         <v>20830.64</v>
       </c>
-      <c r="I30" s="7" t="s">
+      <c r="I31" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J30" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="K30" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="L30" s="7" t="s">
+      <c r="J31" s="7" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="16"/>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="E31" s="18" t="n">
-        <f aca="false">SUM(E30:E30)</f>
+      <c r="K31" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <f aca="false">SUM(E31:E31)</f>
         <v>43760</v>
       </c>
-      <c r="F31" s="19" t="n">
-        <f aca="false">SUM(F30:F30)</f>
+      <c r="F32" s="14" t="n">
+        <f aca="false">SUM(F31:F31)</f>
         <v>957</v>
       </c>
-      <c r="G31" s="19" t="n">
-        <f aca="false">SUM(G30:G30)</f>
+      <c r="G32" s="14" t="n">
+        <f aca="false">SUM(G31:G31)</f>
         <v>1274.42</v>
       </c>
-      <c r="H31" s="19" t="n">
-        <f aca="false">SUM(H30:H30)</f>
+      <c r="H32" s="14" t="n">
+        <f aca="false">SUM(H31:H31)</f>
         <v>20830.64</v>
       </c>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="20"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="E32" s="22" t="n">
-        <f aca="false">E26+E29+E31</f>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="15"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <f aca="false">E27+E30+E32</f>
         <v>1389088</v>
       </c>
-      <c r="F32" s="23" t="n">
-        <f aca="false">F26+F29+F31</f>
+      <c r="F33" s="18" t="n">
+        <f aca="false">F27+F30+F32</f>
         <v>22979.85</v>
       </c>
-      <c r="G32" s="23" t="n">
-        <f aca="false">G26+G29+G31</f>
+      <c r="G33" s="18" t="n">
+        <f aca="false">G27+G30+G32</f>
         <v>24133</v>
       </c>
-      <c r="H32" s="23" t="n">
-        <f aca="false">H26+H29+H31</f>
+      <c r="H33" s="18" t="n">
+        <f aca="false">H27+H30+H32</f>
         <v>119371.08</v>
       </c>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="20"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D34" s="2" t="s">
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="15"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="s">
+      <c r="B35" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B35" s="24" t="n">
-        <f aca="false">E32</f>
-        <v>1389088</v>
-      </c>
-      <c r="C35" s="24" t="n">
-        <v>1389088</v>
-      </c>
-      <c r="D35" s="24" t="n">
-        <f aca="false">B35-C35</f>
-        <v>0</v>
+      <c r="C35" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B36" s="24" t="n">
-        <f aca="false">F32</f>
-        <v>22979.85</v>
-      </c>
-      <c r="C36" s="24" t="n">
-        <v>22979.85</v>
-      </c>
-      <c r="D36" s="24" t="n">
+        <v>85</v>
+      </c>
+      <c r="B36" s="19" t="n">
+        <f aca="false">E33</f>
+        <v>1389088</v>
+      </c>
+      <c r="C36" s="19" t="n">
+        <v>1389088</v>
+      </c>
+      <c r="D36" s="19" t="n">
         <f aca="false">B36-C36</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B37" s="24" t="n">
-        <f aca="false">G32</f>
-        <v>24133</v>
-      </c>
-      <c r="C37" s="24" t="n">
-        <v>24133</v>
-      </c>
-      <c r="D37" s="24" t="n">
+        <v>86</v>
+      </c>
+      <c r="B37" s="19" t="n">
+        <f aca="false">F33</f>
+        <v>22979.85</v>
+      </c>
+      <c r="C37" s="19" t="n">
+        <v>22979.85</v>
+      </c>
+      <c r="D37" s="19" t="n">
         <f aca="false">B37-C37</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B38" s="24" t="n">
-        <f aca="false">H32</f>
+        <v>87</v>
+      </c>
+      <c r="B38" s="19" t="n">
+        <f aca="false">G33</f>
+        <v>24133</v>
+      </c>
+      <c r="C38" s="19" t="n">
+        <v>24133</v>
+      </c>
+      <c r="D38" s="19" t="n">
+        <f aca="false">B38-C38</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B39" s="19" t="n">
+        <f aca="false">H33</f>
         <v>119371.08</v>
       </c>
-      <c r="C38" s="24" t="n">
+      <c r="C39" s="19" t="n">
         <v>119371.08</v>
       </c>
-      <c r="D38" s="24" t="n">
-        <f aca="false">B38-C38</f>
+      <c r="D39" s="19" t="n">
+        <f aca="false">B39-C39</f>
         <v>0</v>
       </c>
     </row>
@@ -2102,85 +2105,94 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
+      <c r="A2" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>94</v>
+        <v>97</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>9</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>210000</v>
@@ -2194,62 +2206,57 @@
       <c r="I5" s="10" t="n">
         <v>8820</v>
       </c>
-      <c r="J5" s="26"/>
+      <c r="J5" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="7" t="n">
+      <c r="A6" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="21" t="n">
         <v>15</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="F6" s="9" t="n">
+      <c r="D6" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6" s="22" t="n">
         <v>30000</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="G6" s="23" t="n">
         <v>12.6</v>
       </c>
-      <c r="H6" s="10" t="n">
+      <c r="H6" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="I6" s="10" t="n">
+      <c r="I6" s="23" t="n">
         <v>540</v>
       </c>
-      <c r="J6" s="26"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E7" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F7" s="27" t="n">
-        <f aca="false">SUM(F5:F6)</f>
-        <v>240000</v>
-      </c>
-      <c r="G7" s="28" t="n">
-        <f aca="false">SUM(G5:G6)</f>
-        <v>42.84</v>
-      </c>
-      <c r="H7" s="28" t="n">
-        <f aca="false">SUM(H5:H6)</f>
-        <v>55</v>
-      </c>
-      <c r="I7" s="28" t="n">
-        <f aca="false">SUM(I5:I6)</f>
-        <v>9360</v>
+      <c r="J6" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="L6" s="21" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2282,64 +2289,64 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="B1" s="29" t="s">
-        <v>101</v>
-      </c>
-      <c r="C1" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="D1" s="29" t="s">
-        <v>90</v>
-      </c>
-      <c r="E1" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="G1" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="H1" s="29" t="s">
-        <v>104</v>
-      </c>
-      <c r="I1" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="J1" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="K1" s="29" t="s">
-        <v>107</v>
-      </c>
-      <c r="L1" s="29" t="s">
+      <c r="A1" s="26" t="s">
         <v>108</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="F1" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="I1" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="J1" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="K1" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="L1" s="26" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H2" s="9" t="n">
         <v>65000</v>
@@ -2354,30 +2361,30 @@
         <v>9841</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C3" s="7" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="H3" s="9" t="n">
         <v>35000</v>
@@ -2392,30 +2399,30 @@
         <v>3542</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C4" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="H4" s="9" t="n">
         <v>32400</v>
@@ -2430,30 +2437,30 @@
         <v>7464.96</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>4</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="H5" s="9" t="n">
         <v>25000</v>
@@ -2468,30 +2475,30 @@
         <v>1377.5</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>5</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="H6" s="9" t="n">
         <v>5600</v>
@@ -2506,30 +2513,30 @@
         <v>449.68</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>6</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="H7" s="9" t="n">
         <v>72000</v>
@@ -2544,30 +2551,30 @@
         <v>7041.6</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>19</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H8" s="9" t="n">
         <v>8000</v>
@@ -2582,30 +2589,30 @@
         <v>2926.4</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>10</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="H9" s="9" t="n">
         <v>75000</v>
@@ -2620,30 +2627,30 @@
         <v>1612.5</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>11</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="H10" s="9" t="n">
         <v>125000</v>
@@ -2658,30 +2665,30 @@
         <v>2687.5</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>12</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="H11" s="9" t="n">
         <v>200000</v>
@@ -2696,30 +2703,30 @@
         <v>2540</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>13</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="H12" s="9" t="n">
         <v>200000</v>
@@ -2734,30 +2741,30 @@
         <v>2540</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>7</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H13" s="9" t="n">
         <v>960</v>
@@ -2772,30 +2779,30 @@
         <v>100.8</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>8</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H14" s="9" t="n">
         <v>2000</v>
@@ -2810,30 +2817,30 @@
         <v>75.8</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>17</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="H15" s="9" t="n">
         <v>5000</v>
@@ -2848,30 +2855,30 @@
         <v>899.5</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>18</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="H16" s="9" t="n">
         <v>2000</v>
@@ -2886,30 +2893,30 @@
         <v>302</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>14</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H17" s="9" t="n">
         <v>180000</v>
@@ -2924,30 +2931,30 @@
         <v>12600</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>16</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H18" s="9" t="n">
         <v>51200</v>
@@ -2962,106 +2969,106 @@
         <v>8120.32</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="11" t="n">
+      <c r="A19" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="D19" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="H19" s="13" t="n">
+      <c r="D19" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="H19" s="9" t="n">
         <v>210000</v>
       </c>
-      <c r="I19" s="14" t="n">
+      <c r="I19" s="10" t="n">
         <v>30.24</v>
       </c>
-      <c r="J19" s="14" t="n">
+      <c r="J19" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="K19" s="14" t="n">
+      <c r="K19" s="10" t="n">
         <v>8820</v>
       </c>
-      <c r="L19" s="11" t="s">
-        <v>63</v>
+      <c r="L19" s="7" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="11" t="n">
+      <c r="A20" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="D20" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="H20" s="13" t="n">
+      <c r="D20" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" s="9" t="n">
         <v>30000</v>
       </c>
-      <c r="I20" s="14" t="n">
+      <c r="I20" s="10" t="n">
         <v>12.6</v>
       </c>
-      <c r="J20" s="14" t="n">
+      <c r="J20" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="K20" s="14" t="n">
+      <c r="K20" s="10" t="n">
         <v>540</v>
       </c>
-      <c r="L20" s="11" t="s">
-        <v>63</v>
+      <c r="L20" s="7" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H21" s="9" t="n">
         <v>19152</v>
@@ -3076,30 +3083,30 @@
         <v>19918.08</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>2</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H22" s="9" t="n">
         <v>2016</v>
@@ -3114,30 +3121,30 @@
         <v>5140.8</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H23" s="9" t="n">
         <v>33600</v>
@@ -3152,30 +3159,30 @@
         <v>16836.96</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C24" s="7" t="n">
         <v>2</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H24" s="9" t="n">
         <v>2160</v>
@@ -3190,30 +3197,30 @@
         <v>1280.88</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C25" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H25" s="9" t="n">
         <v>8000</v>
@@ -3228,36 +3235,36 @@
         <v>2712.8</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="20"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="H26" s="22" t="n">
+      <c r="A26" s="15"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="H26" s="17" t="n">
         <f aca="false">SUM(H2:H25)</f>
         <v>1389088</v>
       </c>
-      <c r="I26" s="23" t="n">
+      <c r="I26" s="18" t="n">
         <f aca="false">SUM(I2:I25)</f>
         <v>22979.85</v>
       </c>
-      <c r="J26" s="23" t="n">
+      <c r="J26" s="18" t="n">
         <f aca="false">SUM(J2:J25)</f>
         <v>24133</v>
       </c>
-      <c r="K26" s="23" t="n">
+      <c r="K26" s="18" t="n">
         <f aca="false">SUM(K2:K25)</f>
         <v>119371.08</v>
       </c>
-      <c r="L26" s="20"/>
+      <c r="L26" s="15"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L25"/>
@@ -3277,7 +3284,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
@@ -3287,194 +3294,238 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="30" t="s">
-        <v>160</v>
-      </c>
-      <c r="B3" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="C3" s="30" t="s">
-        <v>162</v>
+      <c r="A3" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>164</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>165</v>
+      <c r="A4" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="B5" s="31" t="s">
-        <v>166</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>167</v>
+      <c r="A5" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>168</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>169</v>
+      <c r="A6" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>170</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>171</v>
+      <c r="A7" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>172</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>173</v>
+      <c r="A8" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="B9" s="33" t="s">
-        <v>175</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>176</v>
+      <c r="B9" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="B10" s="33" t="s">
-        <v>177</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>178</v>
+      <c r="B10" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="B11" s="33" t="s">
-        <v>180</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="32" t="s">
-        <v>179</v>
-      </c>
-      <c r="B12" s="33" t="s">
-        <v>182</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>183</v>
+      <c r="B12" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="32" t="s">
-        <v>179</v>
-      </c>
-      <c r="B13" s="33" t="s">
-        <v>184</v>
-      </c>
-      <c r="C13" s="32" t="s">
-        <v>185</v>
+      <c r="A13" s="29" t="s">
+        <v>195</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>196</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="32" t="s">
-        <v>179</v>
-      </c>
-      <c r="B14" s="33" t="s">
-        <v>186</v>
-      </c>
-      <c r="C14" s="32" t="s">
-        <v>187</v>
+      <c r="A14" s="29" t="s">
+        <v>195</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="32" t="s">
-        <v>179</v>
-      </c>
-      <c r="B15" s="33" t="s">
-        <v>188</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>189</v>
+      <c r="A15" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>192</v>
+      <c r="A16" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>194</v>
+      <c r="A17" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>205</v>
+      </c>
+      <c r="C17" s="29" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>196</v>
+      <c r="A18" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>207</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>199</v>
+      <c r="A19" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="C19" s="29" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -3502,91 +3553,91 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>202</v>
+        <v>222</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B4" s="35" t="s">
-        <v>204</v>
+        <v>224</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="B5" s="35" t="s">
-        <v>206</v>
+        <v>226</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B6" s="35" t="s">
-        <v>208</v>
+        <v>228</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="B7" s="35" t="s">
-        <v>210</v>
+        <v>230</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>212</v>
+        <v>232</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="B9" s="35" t="s">
-        <v>214</v>
+        <v>234</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B10" s="35" t="s">
-        <v>216</v>
+        <v>236</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B11" s="35" t="s">
-        <v>218</v>
+        <v>238</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3"/>
-      <c r="B12" s="35"/>
+      <c r="B12" s="32"/>
     </row>
     <row r="13" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="B13" s="37" t="s">
-        <v>220</v>
+      <c r="A13" s="33" t="s">
+        <v>240</v>
+      </c>
+      <c r="B13" s="34" t="s">
+        <v>241</v>
       </c>
     </row>
   </sheetData>
